--- a/__andres_control/Mortality Estimates WHO 2024.xlsx
+++ b/__andres_control/Mortality Estimates WHO 2024.xlsx
@@ -571,13 +571,13 @@
         </is>
       </c>
       <c r="E8">
-        <v>3.289493462676341</v>
+        <v>3.654992736307046</v>
       </c>
       <c r="F8">
-        <v>2.076072493482424</v>
+        <v>2.306747214980471</v>
       </c>
       <c r="G8">
-        <v>4.525801345817445</v>
+        <v>5.028668162019384</v>
       </c>
     </row>
     <row r="9">
@@ -598,13 +598,13 @@
         </is>
       </c>
       <c r="E9">
-        <v>3.58672506343983</v>
+        <v>4.69033277526747</v>
       </c>
       <c r="F9">
-        <v>1.518280027864631</v>
+        <v>1.98544311336144</v>
       </c>
       <c r="G9">
-        <v>5.67212031817635</v>
+        <v>7.417388108384457</v>
       </c>
     </row>
     <row r="10">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="E16">
-        <v>5.579276324042212</v>
+        <v>6.774835536336971</v>
       </c>
       <c r="F16">
-        <v>3.648284732901662</v>
+        <v>4.430060032809161</v>
       </c>
       <c r="G16">
-        <v>7.423869850353766</v>
+        <v>9.014699104001002</v>
       </c>
     </row>
     <row r="17">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="E17">
-        <v>2.283829530964693</v>
+        <v>2.569308222335279</v>
       </c>
       <c r="F17">
-        <v>0.9057394571619034</v>
+        <v>1.018956889307141</v>
       </c>
       <c r="G17">
-        <v>3.637508605273806</v>
+        <v>4.092197180933032</v>
       </c>
     </row>
     <row r="18">
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="E24">
-        <v>7.448211525690328</v>
+        <v>9.016256057414608</v>
       </c>
       <c r="F24">
-        <v>4.557509324871589</v>
+        <v>5.516984972212976</v>
       </c>
       <c r="G24">
-        <v>10.13888235898386</v>
+        <v>12.27338390824362</v>
       </c>
     </row>
     <row r="25">
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="E25">
-        <v>3.880567488422228</v>
+        <v>4.203948112457414</v>
       </c>
       <c r="F25">
-        <v>1.609870223908163</v>
+        <v>1.74402607590051</v>
       </c>
       <c r="G25">
-        <v>5.914081314770169</v>
+        <v>6.406921424334349</v>
       </c>
     </row>
     <row r="26">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="E31">
-        <v>5.007248435298941</v>
+        <v>6.933113218106225</v>
       </c>
       <c r="F31">
-        <v>3.031459858967718</v>
+        <v>4.197405958570687</v>
       </c>
       <c r="G31">
-        <v>6.86045797302708</v>
+        <v>9.499095654960572</v>
       </c>
     </row>
     <row r="32">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="E32">
-        <v>2.714471770556182</v>
+        <v>3.73239868451475</v>
       </c>
       <c r="F32">
-        <v>1.191282566816318</v>
+        <v>1.638013529372438</v>
       </c>
       <c r="G32">
-        <v>4.0572633096728</v>
+        <v>5.5787370508001</v>
       </c>
     </row>
     <row r="33">
@@ -1408,13 +1408,13 @@
         </is>
       </c>
       <c r="E39">
-        <v>8.288303174249343</v>
+        <v>9.945963809099212</v>
       </c>
       <c r="F39">
-        <v>5.271019174437487</v>
+        <v>6.325223009324985</v>
       </c>
       <c r="G39">
-        <v>10.98419725761189</v>
+        <v>13.18103670913427</v>
       </c>
     </row>
     <row r="40">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="E40">
-        <v>2.140685935221359</v>
+        <v>3.21102890283204</v>
       </c>
       <c r="F40">
-        <v>0.995217041327815</v>
+        <v>1.492825561991723</v>
       </c>
       <c r="G40">
-        <v>3.160036500202613</v>
+        <v>4.740054750303919</v>
       </c>
     </row>
     <row r="41">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="E47">
-        <v>9.445247417284024</v>
+        <v>10.73323570145912</v>
       </c>
       <c r="F47">
-        <v>6.121724529490406</v>
+        <v>6.956505147148189</v>
       </c>
       <c r="G47">
-        <v>12.49713945805224</v>
+        <v>14.20129483869572</v>
       </c>
     </row>
     <row r="48">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="E48">
-        <v>4.179028436629109</v>
+        <v>4.875533176067295</v>
       </c>
       <c r="F48">
-        <v>1.972659522607486</v>
+        <v>2.301436109708734</v>
       </c>
       <c r="G48">
-        <v>6.163285579343079</v>
+        <v>7.190499842566925</v>
       </c>
     </row>
     <row r="49">
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="E55">
-        <v>6.796969211940754</v>
+        <v>8.496211514925943</v>
       </c>
       <c r="F55">
-        <v>4.258120709336403</v>
+        <v>5.322650886670504</v>
       </c>
       <c r="G55">
-        <v>9.112706124056368</v>
+        <v>11.39088265507046</v>
       </c>
     </row>
     <row r="56">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="E56">
-        <v>3.572337161267579</v>
+        <v>6.430206890281642</v>
       </c>
       <c r="F56">
-        <v>1.740667224041732</v>
+        <v>3.133201003275118</v>
       </c>
       <c r="G56">
-        <v>5.251661525927229</v>
+        <v>9.452990746669013</v>
       </c>
     </row>
     <row r="57">
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="E60">
-        <v>1.951337333037898</v>
+        <v>2.267399013741219</v>
       </c>
       <c r="F60">
-        <v>1.460130267969517</v>
+        <v>1.696630240950495</v>
       </c>
       <c r="G60">
-        <v>2.470902746465953</v>
+        <v>2.871119388499171</v>
       </c>
     </row>
     <row r="61">
@@ -2083,13 +2083,13 @@
         </is>
       </c>
       <c r="E64">
-        <v>2.730988650188554</v>
+        <v>3.576294660961202</v>
       </c>
       <c r="F64">
-        <v>2.1054510491444</v>
+        <v>2.757138278641476</v>
       </c>
       <c r="G64">
-        <v>3.403678167660272</v>
+        <v>4.457197600507499</v>
       </c>
     </row>
     <row r="65">
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="E68">
-        <v>2.462675601583405</v>
+        <v>3.04902693529374</v>
       </c>
       <c r="F68">
-        <v>1.809227141940815</v>
+        <v>2.239995509069581</v>
       </c>
       <c r="G68">
-        <v>3.234319736165991</v>
+        <v>4.00439586382456</v>
       </c>
     </row>
     <row r="69">
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="E72">
-        <v>2.150508074740394</v>
+        <v>2.560802378473759</v>
       </c>
       <c r="F72">
-        <v>1.503354896419184</v>
+        <v>1.790179185867581</v>
       </c>
       <c r="G72">
-        <v>2.897158287653076</v>
+        <v>3.449905592534254</v>
       </c>
     </row>
     <row r="73">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="E76">
-        <v>3.061960578423057</v>
+        <v>3.605503876367978</v>
       </c>
       <c r="F76">
-        <v>2.235748186133293</v>
+        <v>2.632626562369973</v>
       </c>
       <c r="G76">
-        <v>4.012940309316273</v>
+        <v>4.725296577242238</v>
       </c>
     </row>
     <row r="77">
@@ -2515,13 +2515,13 @@
         </is>
       </c>
       <c r="E80">
-        <v>2.69538558186846</v>
+        <v>3.186809472485361</v>
       </c>
       <c r="F80">
-        <v>2.114962850499759</v>
+        <v>2.500563812193086</v>
       </c>
       <c r="G80">
-        <v>3.333501296369676</v>
+        <v>3.941266726094534</v>
       </c>
     </row>
     <row r="81">
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="E84">
-        <v>2.467963772980904</v>
+        <v>2.999343532713635</v>
       </c>
       <c r="F84">
-        <v>1.850522800811895</v>
+        <v>2.248960724431681</v>
       </c>
       <c r="G84">
-        <v>3.110675528222528</v>
+        <v>3.780438201763264</v>
       </c>
     </row>
     <row r="85">
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="E91">
-        <v>29.64709932521043</v>
+        <v>34.32822027129629</v>
       </c>
       <c r="F91">
-        <v>25.37710886715638</v>
+        <v>29.3840207935495</v>
       </c>
       <c r="G91">
-        <v>33.93438049623204</v>
+        <v>39.29244057458448</v>
       </c>
     </row>
     <row r="92">
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="E92">
-        <v>2.565545155002625</v>
+        <v>3.306702644225605</v>
       </c>
       <c r="F92">
-        <v>-5.489287059903081</v>
+        <v>-7.075081099430637</v>
       </c>
       <c r="G92">
-        <v>11.44759833283361</v>
+        <v>14.7546822956522</v>
       </c>
     </row>
     <row r="93">
@@ -3028,13 +3028,13 @@
         </is>
       </c>
       <c r="E99">
-        <v>37.70259937580818</v>
+        <v>48.10331644499664</v>
       </c>
       <c r="F99">
-        <v>32.54268999117431</v>
+        <v>41.51998378184308</v>
       </c>
       <c r="G99">
-        <v>42.70906722966302</v>
+        <v>54.49087887922524</v>
       </c>
     </row>
     <row r="100">
@@ -3055,13 +3055,13 @@
         </is>
       </c>
       <c r="E100">
-        <v>3.888261190816718</v>
+        <v>4.438486831026631</v>
       </c>
       <c r="F100">
-        <v>-6.275426578798359</v>
+        <v>-7.163458641835862</v>
       </c>
       <c r="G100">
-        <v>15.00040611841264</v>
+        <v>17.1231050974333</v>
       </c>
     </row>
     <row r="101">
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="E107">
-        <v>40.82208356418931</v>
+        <v>50.67568994175225</v>
       </c>
       <c r="F107">
-        <v>35.66754601385165</v>
+        <v>44.27695367236756</v>
       </c>
       <c r="G107">
-        <v>45.80698661764414</v>
+        <v>56.86384545638583</v>
       </c>
     </row>
     <row r="108">
@@ -3271,13 +3271,13 @@
         </is>
       </c>
       <c r="E108">
-        <v>3.310196184421474</v>
+        <v>4.012359011419968</v>
       </c>
       <c r="F108">
-        <v>-8.362002449805502</v>
+        <v>-10.13576054521879</v>
       </c>
       <c r="G108">
-        <v>15.28176645222842</v>
+        <v>18.52335327542838</v>
       </c>
     </row>
     <row r="109">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="E115">
-        <v>51.20029919039509</v>
+        <v>60.19494634546449</v>
       </c>
       <c r="F115">
-        <v>44.5920454964723</v>
+        <v>52.42578321882555</v>
       </c>
       <c r="G115">
-        <v>57.77532142253055</v>
+        <v>67.92504005081295</v>
       </c>
     </row>
     <row r="116">
@@ -3487,13 +3487,13 @@
         </is>
       </c>
       <c r="E116">
-        <v>3.930349767979123</v>
+        <v>4.723025351437098</v>
       </c>
       <c r="F116">
-        <v>-11.0057804621775</v>
+        <v>-13.22543366463346</v>
       </c>
       <c r="G116">
-        <v>19.01353555112169</v>
+        <v>22.84819818328068</v>
       </c>
     </row>
     <row r="117">
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="E123">
-        <v>65.20085789070923</v>
+        <v>78.45597735200725</v>
       </c>
       <c r="F123">
-        <v>57.11576107262157</v>
+        <v>68.72720700496771</v>
       </c>
       <c r="G123">
-        <v>72.95627472724129</v>
+        <v>87.78804486409804</v>
       </c>
     </row>
     <row r="124">
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="E124">
-        <v>6.080507991223033</v>
+        <v>7.132903605088558</v>
       </c>
       <c r="F124">
-        <v>-14.37320031513059</v>
+        <v>-16.86086960044166</v>
       </c>
       <c r="G124">
-        <v>26.6315855976887</v>
+        <v>31.24089848959636</v>
       </c>
     </row>
     <row r="125">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="E131">
-        <v>76.62548489609283</v>
+        <v>91.57679902215973</v>
       </c>
       <c r="F131">
-        <v>68.38278092489294</v>
+        <v>81.72576256877448</v>
       </c>
       <c r="G131">
-        <v>84.84808919530511</v>
+        <v>101.4038139163403</v>
       </c>
     </row>
     <row r="132">
@@ -3919,13 +3919,13 @@
         </is>
       </c>
       <c r="E132">
-        <v>5.43929627139433</v>
+        <v>6.754681644215181</v>
       </c>
       <c r="F132">
-        <v>-13.49749649020475</v>
+        <v>-16.76159694862027</v>
       </c>
       <c r="G132">
-        <v>24.74648118642067</v>
+        <v>30.73092434914986</v>
       </c>
     </row>
     <row r="133">
@@ -4108,13 +4108,13 @@
         </is>
       </c>
       <c r="E139">
-        <v>93.25721880056641</v>
+        <v>108.8635288855591</v>
       </c>
       <c r="F139">
-        <v>82.76236641423115</v>
+        <v>96.61239507946985</v>
       </c>
       <c r="G139">
-        <v>103.3252776054761</v>
+        <v>120.6164465108823</v>
       </c>
     </row>
     <row r="140">
@@ -4135,13 +4135,13 @@
         </is>
       </c>
       <c r="E140">
-        <v>5.402359984850404</v>
+        <v>6.489848033748862</v>
       </c>
       <c r="F140">
-        <v>-14.02813447252778</v>
+        <v>-16.85197972349117</v>
       </c>
       <c r="G140">
-        <v>25.39959113735461</v>
+        <v>30.51249584682209</v>
       </c>
     </row>
     <row r="141">
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="E147">
-        <v>9.358287369201408</v>
+        <v>11.92220171692782</v>
       </c>
       <c r="F147">
-        <v>-3.560418178148171</v>
+        <v>-4.535875213257259</v>
       </c>
       <c r="G147">
-        <v>23.76870092408076</v>
+        <v>30.2806737799933</v>
       </c>
     </row>
     <row r="148">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="E148">
-        <v>1.991031058842091</v>
+        <v>2.351611486821367</v>
       </c>
       <c r="F148">
-        <v>-4.44753952698178</v>
+        <v>-5.252999441317063</v>
       </c>
       <c r="G148">
-        <v>8.799276927705835</v>
+        <v>10.39284676500689</v>
       </c>
     </row>
     <row r="149">
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="E155">
-        <v>7.628691991189217</v>
+        <v>9.451476803243278</v>
       </c>
       <c r="F155">
-        <v>-2.885117111094177</v>
+        <v>-3.574481376576857</v>
       </c>
       <c r="G155">
-        <v>18.52780801415897</v>
+        <v>22.9548063892235</v>
       </c>
     </row>
     <row r="156">
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="E156">
-        <v>0.1827691250493078</v>
+        <v>0.241099696873555</v>
       </c>
       <c r="F156">
-        <v>-5.26550910196745</v>
+        <v>-6.945990730254934</v>
       </c>
       <c r="G156">
-        <v>5.856532060381041</v>
+        <v>7.725638037098395</v>
       </c>
     </row>
     <row r="157">
@@ -4756,13 +4756,13 @@
         </is>
       </c>
       <c r="E163">
-        <v>9.260003733129443</v>
+        <v>10.92984047189049</v>
       </c>
       <c r="F163">
-        <v>-4.305938813830326</v>
+        <v>-5.082419583537434</v>
       </c>
       <c r="G163">
-        <v>23.35447281647636</v>
+        <v>27.56593512764422</v>
       </c>
     </row>
     <row r="164">
@@ -4783,13 +4783,13 @@
         </is>
       </c>
       <c r="E164">
-        <v>1.562282902563425</v>
+        <v>2.026327329067413</v>
       </c>
       <c r="F164">
-        <v>-5.279522177280124</v>
+        <v>-6.847697081422735</v>
       </c>
       <c r="G164">
-        <v>8.444383445657042</v>
+        <v>10.95261615228785</v>
       </c>
     </row>
     <row r="165">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="E171">
-        <v>7.63136796142144</v>
+        <v>9.039096031974911</v>
       </c>
       <c r="F171">
-        <v>-3.69302876399796</v>
+        <v>-4.374267079686904</v>
       </c>
       <c r="G171">
-        <v>19.38717240266766</v>
+        <v>22.96344692354811</v>
       </c>
     </row>
     <row r="172">
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="E172">
-        <v>1.963798086509402</v>
+        <v>2.474923615874863</v>
       </c>
       <c r="F172">
-        <v>-3.098159804431446</v>
+        <v>-3.904530164488946</v>
       </c>
       <c r="G172">
-        <v>7.013110365908225</v>
+        <v>8.838440461144613</v>
       </c>
     </row>
     <row r="173">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="E179">
-        <v>9.324684948601442</v>
+        <v>11.26732764622674</v>
       </c>
       <c r="F179">
-        <v>-4.02248008542869</v>
+        <v>-4.860496769893</v>
       </c>
       <c r="G179">
-        <v>22.76166212400641</v>
+        <v>27.50367506650775</v>
       </c>
     </row>
     <row r="180">
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="E180">
-        <v>2.293372495392946</v>
+        <v>2.636060339532122</v>
       </c>
       <c r="F180">
-        <v>-4.012359401107353</v>
+        <v>-4.611907357594658</v>
       </c>
       <c r="G180">
-        <v>8.684068548842321</v>
+        <v>9.981687987175082</v>
       </c>
     </row>
     <row r="181">
@@ -5404,13 +5404,13 @@
         </is>
       </c>
       <c r="E187">
-        <v>13.10933938038199</v>
+        <v>16.32483771896625</v>
       </c>
       <c r="F187">
-        <v>-5.977730246695405</v>
+        <v>-7.443965967582956</v>
       </c>
       <c r="G187">
-        <v>32.52727620717207</v>
+        <v>40.50566471081805</v>
       </c>
     </row>
     <row r="188">
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="E188">
-        <v>2.402374701750305</v>
+        <v>3.151166816581568</v>
       </c>
       <c r="F188">
-        <v>-2.785126403973242</v>
+        <v>-3.6532177506662</v>
       </c>
       <c r="G188">
-        <v>7.673096246245249</v>
+        <v>10.06471066065935</v>
       </c>
     </row>
     <row r="189">
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="E195">
-        <v>12.20854355497865</v>
+        <v>15.00633478632792</v>
       </c>
       <c r="F195">
-        <v>-6.283399813093951</v>
+        <v>-7.723345603594648</v>
       </c>
       <c r="G195">
-        <v>30.30995952844396</v>
+        <v>37.25599192037903</v>
       </c>
     </row>
     <row r="196">
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="E196">
-        <v>3.646379359735808</v>
+        <v>4.465790451811271</v>
       </c>
       <c r="F196">
-        <v>-2.323179489460999</v>
+        <v>-2.845242296081449</v>
       </c>
       <c r="G196">
-        <v>9.787558976094495</v>
+        <v>11.98701043139663</v>
       </c>
     </row>
     <row r="197">
@@ -5836,13 +5836,13 @@
         </is>
       </c>
       <c r="E203">
-        <v>0.8670015180267004</v>
+        <v>1.156002024035601</v>
       </c>
       <c r="F203">
-        <v>0.5819124870473523</v>
+        <v>0.7758833160631364</v>
       </c>
       <c r="G203">
-        <v>1.206827458821242</v>
+        <v>1.609103278428323</v>
       </c>
     </row>
     <row r="204">
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="E204">
-        <v>0.2362603470344137</v>
+        <v>0.2887626463753945</v>
       </c>
       <c r="F204">
-        <v>0.1524694230802754</v>
+        <v>0.1863515170981144</v>
       </c>
       <c r="G204">
-        <v>0.3428679877434744</v>
+        <v>0.419060873908691</v>
       </c>
     </row>
     <row r="205">
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c r="E211">
-        <v>1.811995551732759</v>
+        <v>1.941423805427956</v>
       </c>
       <c r="F211">
-        <v>1.212881761737741</v>
+        <v>1.299516173290437</v>
       </c>
       <c r="G211">
-        <v>2.509553348291389</v>
+        <v>2.688807158883631</v>
       </c>
     </row>
     <row r="212">
@@ -6079,13 +6079,13 @@
         </is>
       </c>
       <c r="E212">
-        <v>0.2456577645840322</v>
+        <v>0.4094296076400536</v>
       </c>
       <c r="F212">
-        <v>0.1658414872935706</v>
+        <v>0.2764024788226176</v>
       </c>
       <c r="G212">
-        <v>0.3446605013496631</v>
+        <v>0.5744341689161052</v>
       </c>
     </row>
     <row r="213">
@@ -6268,13 +6268,13 @@
         </is>
       </c>
       <c r="E219">
-        <v>1.176504468830085</v>
+        <v>1.260540502317948</v>
       </c>
       <c r="F219">
-        <v>0.7953482827111531</v>
+        <v>0.8521588743333783</v>
       </c>
       <c r="G219">
-        <v>1.645830768439651</v>
+        <v>1.763390109042484</v>
       </c>
     </row>
     <row r="220">
@@ -6484,13 +6484,13 @@
         </is>
       </c>
       <c r="E227">
-        <v>1.056618900955065</v>
+        <v>1.219175654948151</v>
       </c>
       <c r="F227">
-        <v>0.73023364992065</v>
+        <v>0.8425772883699807</v>
       </c>
       <c r="G227">
-        <v>1.45271251513984</v>
+        <v>1.676206748238277</v>
       </c>
     </row>
     <row r="228">
@@ -6511,13 +6511,13 @@
         </is>
       </c>
       <c r="E228">
-        <v>0.2816605473835876</v>
+        <v>0.3990191087934158</v>
       </c>
       <c r="F228">
-        <v>0.176958761703881</v>
+        <v>0.2506915790804981</v>
       </c>
       <c r="G228">
-        <v>0.4246656370318014</v>
+        <v>0.6016096524617187</v>
       </c>
     </row>
     <row r="229">
@@ -6700,13 +6700,13 @@
         </is>
       </c>
       <c r="E235">
-        <v>2.744592138331655</v>
+        <v>3.430740172914569</v>
       </c>
       <c r="F235">
-        <v>1.789811881391072</v>
+        <v>2.23726485173884</v>
       </c>
       <c r="G235">
-        <v>3.907872458843281</v>
+        <v>4.884840573554101</v>
       </c>
     </row>
     <row r="236">
@@ -6916,13 +6916,13 @@
         </is>
       </c>
       <c r="E243">
-        <v>1.983921249118122</v>
+        <v>2.424792637811039</v>
       </c>
       <c r="F243">
-        <v>1.316409433040282</v>
+        <v>1.60894486260479</v>
       </c>
       <c r="G243">
-        <v>2.775917419353827</v>
+        <v>3.392787956988011</v>
       </c>
     </row>
     <row r="244">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="E244">
-        <v>0.3933427504608495</v>
+        <v>0.4495345719552566</v>
       </c>
       <c r="F244">
-        <v>0.2646363500041376</v>
+        <v>0.3024415428618715</v>
       </c>
       <c r="G244">
-        <v>0.5539522638746858</v>
+        <v>0.6330883015710694</v>
       </c>
     </row>
     <row r="245">
@@ -7132,13 +7132,13 @@
         </is>
       </c>
       <c r="E251">
-        <v>2.149899613969589</v>
+        <v>2.418637065715787</v>
       </c>
       <c r="F251">
-        <v>1.444061414625229</v>
+        <v>1.624569091453382</v>
       </c>
       <c r="G251">
-        <v>2.9953681543065</v>
+        <v>3.369789173594812</v>
       </c>
     </row>
     <row r="252">
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="E252">
-        <v>0.4299745409060802</v>
+        <v>0.5732993878747736</v>
       </c>
       <c r="F252">
-        <v>0.2569877905090769</v>
+        <v>0.3426503873454359</v>
       </c>
       <c r="G252">
-        <v>0.6486225096049698</v>
+        <v>0.8648300128066264</v>
       </c>
     </row>
     <row r="253">
@@ -7348,13 +7348,13 @@
         </is>
       </c>
       <c r="E259">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F259">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G259">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="260">
@@ -7564,13 +7564,13 @@
         </is>
       </c>
       <c r="E267">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F267">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G267">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="268">
@@ -7753,13 +7753,13 @@
         </is>
       </c>
       <c r="E274">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F274">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G274">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="275">
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="E282">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F282">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G282">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="283">
@@ -7996,13 +7996,13 @@
         </is>
       </c>
       <c r="E283">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F283">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G283">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284">
@@ -8185,13 +8185,13 @@
         </is>
       </c>
       <c r="E290">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F290">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G290">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="291">
@@ -8374,13 +8374,13 @@
         </is>
       </c>
       <c r="E297">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F297">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G297">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="298">
@@ -8563,13 +8563,13 @@
         </is>
       </c>
       <c r="E304">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F304">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G304">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="305">
@@ -8752,13 +8752,13 @@
         </is>
       </c>
       <c r="E311">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F311">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G311">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="312">
@@ -8941,13 +8941,13 @@
         </is>
       </c>
       <c r="E318">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F318">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G318">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="319">
@@ -8968,13 +8968,13 @@
         </is>
       </c>
       <c r="E319">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F319">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G319">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -9130,13 +9130,13 @@
         </is>
       </c>
       <c r="E325">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F325">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="G325">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="326">
@@ -9157,13 +9157,13 @@
         </is>
       </c>
       <c r="E326">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F326">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G326">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="327">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="E333">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F333">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G333">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="334">
@@ -9373,13 +9373,13 @@
         </is>
       </c>
       <c r="E334">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F334">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G334">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="335">
@@ -9562,13 +9562,13 @@
         </is>
       </c>
       <c r="E341">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F341">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G341">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="342">
@@ -9751,13 +9751,13 @@
         </is>
       </c>
       <c r="E348">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F348">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G348">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="349">
@@ -9778,13 +9778,13 @@
         </is>
       </c>
       <c r="E349">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F349">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G349">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350">
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="E356">
-        <v>0.1211530819509494</v>
+        <v>0.1557682482226492</v>
       </c>
       <c r="F356">
-        <v>0.04774780723459349</v>
+        <v>0.06139003787304877</v>
       </c>
       <c r="G356">
-        <v>0.2250431720261664</v>
+        <v>0.2893412211764996</v>
       </c>
     </row>
     <row r="357">
@@ -10183,13 +10183,13 @@
         </is>
       </c>
       <c r="E364">
-        <v>0.3579389245306015</v>
+        <v>0.4201891722750539</v>
       </c>
       <c r="F364">
-        <v>0.1540442104650537</v>
+        <v>0.180834507937237</v>
       </c>
       <c r="G364">
-        <v>0.6161768625470097</v>
+        <v>0.7233380560334461</v>
       </c>
     </row>
     <row r="365">
@@ -10399,13 +10399,13 @@
         </is>
       </c>
       <c r="E372">
-        <v>0.1606274067006545</v>
+        <v>0.1950475652793662</v>
       </c>
       <c r="F372">
-        <v>0.0505516115501872</v>
+        <v>0.06138409973951302</v>
       </c>
       <c r="G372">
-        <v>0.3352834725496405</v>
+        <v>0.4071299309531349</v>
       </c>
     </row>
     <row r="373">
@@ -10426,13 +10426,13 @@
         </is>
       </c>
       <c r="E373">
-        <v>0.001366134792702836</v>
+        <v>0.001561296905946098</v>
       </c>
       <c r="F373">
-        <v>6.436026478820799E-05</v>
+        <v>7.355458832938055E-05</v>
       </c>
       <c r="G373">
-        <v>0.007635188415748341</v>
+        <v>0.008725929617998104</v>
       </c>
     </row>
     <row r="374">
@@ -10615,13 +10615,13 @@
         </is>
       </c>
       <c r="E380">
-        <v>0.07005793252109738</v>
+        <v>0.09161421945066579</v>
       </c>
       <c r="F380">
-        <v>0.02736835591669891</v>
+        <v>0.03578938850645242</v>
       </c>
       <c r="G380">
-        <v>0.1374918861490597</v>
+        <v>0.1797970818872319</v>
       </c>
     </row>
     <row r="381">
@@ -10831,13 +10831,13 @@
         </is>
       </c>
       <c r="E388">
-        <v>0.1513225027540109</v>
+        <v>0.2161750039343012</v>
       </c>
       <c r="F388">
-        <v>0.04519700499225968</v>
+        <v>0.0645671499889424</v>
       </c>
       <c r="G388">
-        <v>0.3042199067168119</v>
+        <v>0.4345998667383028</v>
       </c>
     </row>
     <row r="389">
@@ -10858,13 +10858,13 @@
         </is>
       </c>
       <c r="E389">
-        <v>0.005622139056325622</v>
+        <v>0.01311832446475979</v>
       </c>
       <c r="F389">
-        <v>0.0006783381702325905</v>
+        <v>0.001582789063876045</v>
       </c>
       <c r="G389">
-        <v>0.0170205903914659</v>
+        <v>0.03971471091342044</v>
       </c>
     </row>
     <row r="390">
@@ -11047,13 +11047,13 @@
         </is>
       </c>
       <c r="E396">
-        <v>0.3317976359840484</v>
+        <v>0.3456225374833838</v>
       </c>
       <c r="F396">
-        <v>0.147813216930146</v>
+        <v>0.153972100968902</v>
       </c>
       <c r="G396">
-        <v>0.5659398593307231</v>
+        <v>0.5895206868028365</v>
       </c>
     </row>
     <row r="397">
@@ -11074,13 +11074,13 @@
         </is>
       </c>
       <c r="E397">
-        <v>0.005883421563173357</v>
+        <v>0.009805702605288928</v>
       </c>
       <c r="F397">
-        <v>0.001649384489717952</v>
+        <v>0.002748974149529921</v>
       </c>
       <c r="G397">
-        <v>0.01322544651513209</v>
+        <v>0.02204241085855348</v>
       </c>
     </row>
     <row r="398">
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="E404">
-        <v>0.1941324107200683</v>
+        <v>0.204917544648961</v>
       </c>
       <c r="F404">
-        <v>0.09574626369271393</v>
+        <v>0.1010655005645314</v>
       </c>
       <c r="G404">
-        <v>0.3192688911221413</v>
+        <v>0.3370060517400381</v>
       </c>
     </row>
     <row r="405">
@@ -11290,13 +11290,13 @@
         </is>
       </c>
       <c r="E405">
-        <v>0.01200576149988696</v>
+        <v>0.01600768199984928</v>
       </c>
       <c r="F405">
-        <v>0.004379012144321408</v>
+        <v>0.00583868285909521</v>
       </c>
       <c r="G405">
-        <v>0.02228808450204811</v>
+        <v>0.02971744600273081</v>
       </c>
     </row>
     <row r="406">
@@ -11479,13 +11479,13 @@
         </is>
       </c>
       <c r="E412">
-        <v>7.900122304347122</v>
+        <v>9.02871120496814</v>
       </c>
       <c r="F412">
-        <v>1.062022351439587</v>
+        <v>1.213739830216671</v>
       </c>
       <c r="G412">
-        <v>15.23111545473603</v>
+        <v>17.4069890911269</v>
       </c>
     </row>
     <row r="413">
@@ -11506,13 +11506,13 @@
         </is>
       </c>
       <c r="E413">
-        <v>0.6053629943246416</v>
+        <v>0.7410478033974062</v>
       </c>
       <c r="F413">
-        <v>0.2470550942739415</v>
+        <v>0.3024295119560318</v>
       </c>
       <c r="G413">
-        <v>1.027810281228171</v>
+        <v>1.258181551158623</v>
       </c>
     </row>
     <row r="414">
@@ -11695,13 +11695,13 @@
         </is>
       </c>
       <c r="E420">
-        <v>12.66237928821677</v>
+        <v>14.87608196098194</v>
       </c>
       <c r="F420">
-        <v>3.038776988067077</v>
+        <v>3.570031706260623</v>
       </c>
       <c r="G420">
-        <v>22.37481149751575</v>
+        <v>26.28649182924927</v>
       </c>
     </row>
     <row r="421">
@@ -11722,13 +11722,13 @@
         </is>
       </c>
       <c r="E421">
-        <v>1.369656012490252</v>
+        <v>1.831708643209856</v>
       </c>
       <c r="F421">
-        <v>0.5629777494607007</v>
+        <v>0.7528979540980454</v>
       </c>
       <c r="G421">
-        <v>2.262655865446335</v>
+        <v>3.025961458608953</v>
       </c>
     </row>
     <row r="422">
@@ -11884,13 +11884,13 @@
         </is>
       </c>
       <c r="E427">
-        <v>10.29358235519587</v>
+        <v>11.87143074540837</v>
       </c>
       <c r="F427">
-        <v>-0.7726339139598051</v>
+        <v>-0.8910668496762716</v>
       </c>
       <c r="G427">
-        <v>21.7303543403052</v>
+        <v>25.06128456765125</v>
       </c>
     </row>
     <row r="428">
@@ -11911,13 +11911,13 @@
         </is>
       </c>
       <c r="E428">
-        <v>0.9215907814214772</v>
+        <v>1.151988476776846</v>
       </c>
       <c r="F428">
-        <v>0.3191651996265618</v>
+        <v>0.3989564995332022</v>
       </c>
       <c r="G428">
-        <v>1.607485070466655</v>
+        <v>2.009356338083319</v>
       </c>
     </row>
     <row r="429">
@@ -12073,13 +12073,13 @@
         </is>
       </c>
       <c r="E434">
-        <v>10.19564712212379</v>
+        <v>13.05629631466212</v>
       </c>
       <c r="F434">
-        <v>-0.8919048888061457</v>
+        <v>-1.142151584226575</v>
       </c>
       <c r="G434">
-        <v>21.52828704258748</v>
+        <v>27.56859779554368</v>
       </c>
     </row>
     <row r="435">
@@ -12100,13 +12100,13 @@
         </is>
       </c>
       <c r="E435">
-        <v>0.7026243423348626</v>
+        <v>0.8566241981890791</v>
       </c>
       <c r="F435">
-        <v>0.2354083433368248</v>
+        <v>0.2870046925613344</v>
       </c>
       <c r="G435">
-        <v>1.255824722437965</v>
+        <v>1.531073976670943</v>
       </c>
     </row>
     <row r="436">
@@ -12289,13 +12289,13 @@
         </is>
       </c>
       <c r="E442">
-        <v>14.75586617053549</v>
+        <v>18.2226058130107</v>
       </c>
       <c r="F442">
-        <v>1.231215854202576</v>
+        <v>1.52047741031041</v>
       </c>
       <c r="G442">
-        <v>28.16831650232614</v>
+        <v>34.7861739938365</v>
       </c>
     </row>
     <row r="443">
@@ -12316,13 +12316,13 @@
         </is>
       </c>
       <c r="E443">
-        <v>1.322744057475084</v>
+        <v>1.710214538957685</v>
       </c>
       <c r="F443">
-        <v>0.5191333425221496</v>
+        <v>0.6712027054831833</v>
       </c>
       <c r="G443">
-        <v>2.306317667162577</v>
+        <v>2.981905670674847</v>
       </c>
     </row>
     <row r="444">
@@ -12505,13 +12505,13 @@
         </is>
       </c>
       <c r="E450">
-        <v>13.3204006699861</v>
+        <v>16.35139004399491</v>
       </c>
       <c r="F450">
-        <v>-1.399052614096075</v>
+        <v>-1.717399915507158</v>
       </c>
       <c r="G450">
-        <v>28.11101893580706</v>
+        <v>34.50753821461345</v>
       </c>
     </row>
     <row r="451">
@@ -12532,13 +12532,13 @@
         </is>
       </c>
       <c r="E451">
-        <v>1.207498927693671</v>
+        <v>1.613760249160701</v>
       </c>
       <c r="F451">
-        <v>0.5105695303498421</v>
+        <v>0.6823499330843684</v>
       </c>
       <c r="G451">
-        <v>1.998491778648679</v>
+        <v>2.670881535951039</v>
       </c>
     </row>
     <row r="452">
@@ -12721,13 +12721,13 @@
         </is>
       </c>
       <c r="E458">
-        <v>11.92313333032225</v>
+        <v>14.58830431004134</v>
       </c>
       <c r="F458">
-        <v>-3.997643295421863</v>
+        <v>-4.891234149692632</v>
       </c>
       <c r="G458">
-        <v>27.97239508404325</v>
+        <v>34.22504810282939</v>
       </c>
     </row>
     <row r="459">
@@ -12748,13 +12748,13 @@
         </is>
       </c>
       <c r="E459">
-        <v>1.122161511822003</v>
+        <v>1.424281918851004</v>
       </c>
       <c r="F459">
-        <v>0.4938434543669125</v>
+        <v>0.6268013074656966</v>
       </c>
       <c r="G459">
-        <v>1.883142901324846</v>
+        <v>2.390142913219997</v>
       </c>
     </row>
     <row r="460">
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="E466">
-        <v>12.23269587343369</v>
+        <v>14.11464908473118</v>
       </c>
       <c r="F466">
-        <v>2.483556986837819</v>
+        <v>2.86564267712056</v>
       </c>
       <c r="G466">
-        <v>24.55115662199325</v>
+        <v>28.32825764076144</v>
       </c>
     </row>
     <row r="467">
@@ -12964,13 +12964,13 @@
         </is>
       </c>
       <c r="E467">
-        <v>0.6854252063422358</v>
+        <v>0.806382595696748</v>
       </c>
       <c r="F467">
-        <v>0.1268144846772326</v>
+        <v>0.1491935113849796</v>
       </c>
       <c r="G467">
-        <v>1.561129509063488</v>
+        <v>1.836622951839398</v>
       </c>
     </row>
     <row r="468">
@@ -13153,13 +13153,13 @@
         </is>
       </c>
       <c r="E474">
-        <v>15.22723020895137</v>
+        <v>16.8693824863873</v>
       </c>
       <c r="F474">
-        <v>3.398498082993311</v>
+        <v>3.76500277821808</v>
       </c>
       <c r="G474">
-        <v>29.66637510888796</v>
+        <v>32.86569007161116</v>
       </c>
     </row>
     <row r="475">
@@ -13180,13 +13180,13 @@
         </is>
       </c>
       <c r="E475">
-        <v>1.256075711602013</v>
+        <v>1.570094639502517</v>
       </c>
       <c r="F475">
-        <v>0.2313005945517471</v>
+        <v>0.2891257431896839</v>
       </c>
       <c r="G475">
-        <v>2.764277437452711</v>
+        <v>3.455346796815888</v>
       </c>
     </row>
     <row r="476">
@@ -13369,13 +13369,13 @@
         </is>
       </c>
       <c r="E482">
-        <v>13.06260504062167</v>
+        <v>15.65047962414106</v>
       </c>
       <c r="F482">
-        <v>2.471978197715077</v>
+        <v>2.961709727451083</v>
       </c>
       <c r="G482">
-        <v>26.50962752867647</v>
+        <v>31.76153486926332</v>
       </c>
     </row>
     <row r="483">
@@ -13396,13 +13396,13 @@
         </is>
       </c>
       <c r="E483">
-        <v>1.450145925245349</v>
+        <v>1.526469394995104</v>
       </c>
       <c r="F483">
-        <v>0.2250931273495855</v>
+        <v>0.2369401340521952</v>
       </c>
       <c r="G483">
-        <v>3.134823203679736</v>
+        <v>3.299813898610248</v>
       </c>
     </row>
     <row r="484">
@@ -13585,13 +13585,13 @@
         </is>
       </c>
       <c r="E490">
-        <v>14.99697294611219</v>
+        <v>16.64801583926215</v>
       </c>
       <c r="F490">
-        <v>2.8344395726915</v>
+        <v>3.146487966015335</v>
       </c>
       <c r="G490">
-        <v>29.91044298926345</v>
+        <v>33.20333579542089</v>
       </c>
     </row>
     <row r="491">
@@ -13612,13 +13612,13 @@
         </is>
       </c>
       <c r="E491">
-        <v>0.7958541426057599</v>
+        <v>1.3264235710096</v>
       </c>
       <c r="F491">
-        <v>0.1210309705917335</v>
+        <v>0.2017182843195559</v>
       </c>
       <c r="G491">
-        <v>1.7287859596477</v>
+        <v>2.881309932746167</v>
       </c>
     </row>
     <row r="492">
@@ -13801,13 +13801,13 @@
         </is>
       </c>
       <c r="E498">
-        <v>15.90988849528148</v>
+        <v>17.84286560218483</v>
       </c>
       <c r="F498">
-        <v>3.295274350512752</v>
+        <v>3.695634785621778</v>
       </c>
       <c r="G498">
-        <v>31.04081924572361</v>
+        <v>34.81213373352181</v>
       </c>
     </row>
     <row r="499">
@@ -13828,13 +13828,13 @@
         </is>
       </c>
       <c r="E499">
-        <v>1.69100312025894</v>
+        <v>1.756041701807361</v>
       </c>
       <c r="F499">
-        <v>0.2952358797133492</v>
+        <v>0.3065911058561703</v>
       </c>
       <c r="G499">
-        <v>3.731952437259205</v>
+        <v>3.875489069461483</v>
       </c>
     </row>
     <row r="500">
@@ -14017,13 +14017,13 @@
         </is>
       </c>
       <c r="E506">
-        <v>18.70669659408209</v>
+        <v>21.02796551451564</v>
       </c>
       <c r="F506">
-        <v>4.058035308165317</v>
+        <v>4.561587134725976</v>
       </c>
       <c r="G506">
-        <v>37.06243412087726</v>
+        <v>41.66142229646056</v>
       </c>
     </row>
     <row r="507">
@@ -14044,13 +14044,13 @@
         </is>
       </c>
       <c r="E507">
-        <v>1.522300178939567</v>
+        <v>1.765868207569897</v>
       </c>
       <c r="F507">
-        <v>0.243438200159941</v>
+        <v>0.2823883121855316</v>
       </c>
       <c r="G507">
-        <v>3.396556282493205</v>
+        <v>3.940005287692118</v>
       </c>
     </row>
     <row r="508">
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="E514">
-        <v>11.09232189779949</v>
+        <v>12.45453686770469</v>
       </c>
       <c r="F514">
-        <v>2.245939397793206</v>
+        <v>2.521756516820442</v>
       </c>
       <c r="G514">
-        <v>22.48705385445827</v>
+        <v>25.24862187167245</v>
       </c>
     </row>
     <row r="515">
@@ -14260,13 +14260,13 @@
         </is>
       </c>
       <c r="E515">
-        <v>0.6702810557925269</v>
+        <v>0.8378513197406587</v>
       </c>
       <c r="F515">
-        <v>0.1196826555285811</v>
+        <v>0.1496033194107264</v>
       </c>
       <c r="G515">
-        <v>1.525718806593609</v>
+        <v>1.907148508242011</v>
       </c>
     </row>
     <row r="516">
@@ -14449,13 +14449,13 @@
         </is>
       </c>
       <c r="E522">
-        <v>19.31907329083436</v>
+        <v>23.74328854827735</v>
       </c>
       <c r="F522">
-        <v>3.13817403320727</v>
+        <v>3.856839842338706</v>
       </c>
       <c r="G522">
-        <v>37.38921259476653</v>
+        <v>45.95162769280466</v>
       </c>
     </row>
     <row r="523">
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="E523">
-        <v>14.63629015912049</v>
+        <v>17.24991340182058</v>
       </c>
       <c r="F523">
-        <v>0.251200936143441</v>
+        <v>0.2960582461690554</v>
       </c>
       <c r="G523">
-        <v>30.30354565481386</v>
+        <v>35.71489309317348</v>
       </c>
     </row>
     <row r="524">
@@ -14665,13 +14665,13 @@
         </is>
       </c>
       <c r="E530">
-        <v>24.06379276690767</v>
+        <v>29.5919613755216</v>
       </c>
       <c r="F530">
-        <v>5.218402448706331</v>
+        <v>6.417224632868596</v>
       </c>
       <c r="G530">
-        <v>43.68125028754323</v>
+        <v>53.71613211035721</v>
       </c>
     </row>
     <row r="531">
@@ -14692,13 +14692,13 @@
         </is>
       </c>
       <c r="E531">
-        <v>14.89792102074414</v>
+        <v>19.41244254218176</v>
       </c>
       <c r="F531">
-        <v>1.610246515554904</v>
+        <v>2.098200005116996</v>
       </c>
       <c r="G531">
-        <v>29.34680565574742</v>
+        <v>38.23977706657997</v>
       </c>
     </row>
     <row r="532">
@@ -14881,13 +14881,13 @@
         </is>
       </c>
       <c r="E538">
-        <v>23.22084600031777</v>
+        <v>27.1454960285405</v>
       </c>
       <c r="F538">
-        <v>1.388487122963838</v>
+        <v>1.623161002901388</v>
       </c>
       <c r="G538">
-        <v>45.67033143744167</v>
+        <v>53.38926069447407</v>
       </c>
     </row>
     <row r="539">
@@ -14908,13 +14908,13 @@
         </is>
       </c>
       <c r="E539">
-        <v>14.62434908676281</v>
+        <v>16.49128726805167</v>
       </c>
       <c r="F539">
-        <v>-0.6071549543615804</v>
+        <v>-0.6846640974715693</v>
       </c>
       <c r="G539">
-        <v>29.80284248448372</v>
+        <v>33.60746067399227</v>
       </c>
     </row>
     <row r="540">
@@ -15097,13 +15097,13 @@
         </is>
       </c>
       <c r="E546">
-        <v>19.00744841786055</v>
+        <v>24.43814796582071</v>
       </c>
       <c r="F546">
-        <v>0.9518497459190609</v>
+        <v>1.22380681618165</v>
       </c>
       <c r="G546">
-        <v>37.66639872282964</v>
+        <v>48.42822692935239</v>
       </c>
     </row>
     <row r="547">
@@ -15124,13 +15124,13 @@
         </is>
       </c>
       <c r="E547">
-        <v>16.22738958361345</v>
+        <v>20.04559889740486</v>
       </c>
       <c r="F547">
-        <v>-1.240036804520993</v>
+        <v>-1.531810170290639</v>
       </c>
       <c r="G547">
-        <v>33.31211167274512</v>
+        <v>41.15025559574397</v>
       </c>
     </row>
     <row r="548">
@@ -15313,13 +15313,13 @@
         </is>
       </c>
       <c r="E554">
-        <v>19.95631331281432</v>
+        <v>25.38303009086032</v>
       </c>
       <c r="F554">
-        <v>2.840311586254297</v>
+        <v>3.61267701760415</v>
       </c>
       <c r="G554">
-        <v>37.25704462163346</v>
+        <v>47.38834622927063</v>
       </c>
     </row>
     <row r="555">
@@ -15340,13 +15340,13 @@
         </is>
       </c>
       <c r="E555">
-        <v>15.12358630928193</v>
+        <v>19.34412202350014</v>
       </c>
       <c r="F555">
-        <v>0.2229931822431587</v>
+        <v>0.2852238377528774</v>
       </c>
       <c r="G555">
-        <v>29.66706601089657</v>
+        <v>37.9462472232398</v>
       </c>
     </row>
     <row r="556">
@@ -15529,13 +15529,13 @@
         </is>
       </c>
       <c r="E562">
-        <v>20.9726479539813</v>
+        <v>26.21580994247662</v>
       </c>
       <c r="F562">
-        <v>2.08990939133042</v>
+        <v>2.612386739163025</v>
       </c>
       <c r="G562">
-        <v>39.77496570435162</v>
+        <v>49.71870713043953</v>
       </c>
     </row>
     <row r="563">
@@ -15556,13 +15556,13 @@
         </is>
       </c>
       <c r="E563">
-        <v>16.28736392109912</v>
+        <v>19.27892055966834</v>
       </c>
       <c r="F563">
-        <v>0.02694605817076106</v>
+        <v>0.03189533416130901</v>
       </c>
       <c r="G563">
-        <v>32.47721735904861</v>
+        <v>38.44242054744529</v>
       </c>
     </row>
     <row r="564">
@@ -15745,13 +15745,13 @@
         </is>
       </c>
       <c r="E570">
-        <v>24.68090200275134</v>
+        <v>29.33092701776247</v>
       </c>
       <c r="F570">
-        <v>0.6615538702254878</v>
+        <v>0.7861944544708697</v>
       </c>
       <c r="G570">
-        <v>47.9703222201145</v>
+        <v>57.00820901520854</v>
       </c>
     </row>
     <row r="571">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="E571">
-        <v>17.71942215962273</v>
+        <v>20.39405191956579</v>
       </c>
       <c r="F571">
-        <v>-0.2762182820998147</v>
+        <v>-0.3179116076997868</v>
       </c>
       <c r="G571">
-        <v>35.71246208693004</v>
+        <v>41.10302240193835</v>
       </c>
     </row>
     <row r="572">
@@ -15961,13 +15961,13 @@
         </is>
       </c>
       <c r="E578">
-        <v>25.76721233263551</v>
+        <v>32.77945586160327</v>
       </c>
       <c r="F578">
-        <v>8.905852225192112</v>
+        <v>11.32947507697225</v>
       </c>
       <c r="G578">
-        <v>43.89577303523441</v>
+        <v>55.84149096706926</v>
       </c>
     </row>
     <row r="579">
@@ -15988,13 +15988,13 @@
         </is>
       </c>
       <c r="E579">
-        <v>24.23095044907273</v>
+        <v>30.57044329912083</v>
       </c>
       <c r="F579">
-        <v>6.266908465759007</v>
+        <v>7.906506610870376</v>
       </c>
       <c r="G579">
-        <v>43.15638521589608</v>
+        <v>54.44729995261308</v>
       </c>
     </row>
     <row r="580">
@@ -16177,13 +16177,13 @@
         </is>
       </c>
       <c r="E586">
-        <v>29.32374607960259</v>
+        <v>36.04836454146634</v>
       </c>
       <c r="F586">
-        <v>7.941770793126644</v>
+        <v>9.763003944933882</v>
       </c>
       <c r="G586">
-        <v>51.02371988041665</v>
+        <v>62.72464812367009</v>
       </c>
     </row>
     <row r="587">
@@ -16204,13 +16204,13 @@
         </is>
       </c>
       <c r="E587">
-        <v>24.40838363871948</v>
+        <v>30.83933501658569</v>
       </c>
       <c r="F587">
-        <v>6.060962631101917</v>
+        <v>7.657862965044937</v>
       </c>
       <c r="G587">
-        <v>43.71468357352811</v>
+        <v>55.23232475457743</v>
       </c>
     </row>
     <row r="588">
@@ -16393,13 +16393,13 @@
         </is>
       </c>
       <c r="E594">
-        <v>34.82661495264934</v>
+        <v>42.56586271990475</v>
       </c>
       <c r="F594">
-        <v>13.45591498987049</v>
+        <v>16.44611832095282</v>
       </c>
       <c r="G594">
-        <v>56.62519358290518</v>
+        <v>69.20856993466188</v>
       </c>
     </row>
     <row r="595">
@@ -16420,13 +16420,13 @@
         </is>
       </c>
       <c r="E595">
-        <v>30.28394666412975</v>
+        <v>37.6788638728126</v>
       </c>
       <c r="F595">
-        <v>9.524271048706622</v>
+        <v>11.84996514199545</v>
       </c>
       <c r="G595">
-        <v>51.78411287802452</v>
+        <v>64.4290706738212</v>
       </c>
     </row>
     <row r="596">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="E602">
-        <v>37.39223899245147</v>
+        <v>45.09476013321864</v>
       </c>
       <c r="F602">
-        <v>14.55556051942724</v>
+        <v>17.55389695601338</v>
       </c>
       <c r="G602">
-        <v>60.72084055954711</v>
+        <v>73.2288788770568</v>
       </c>
     </row>
     <row r="603">
@@ -16636,13 +16636,13 @@
         </is>
       </c>
       <c r="E603">
-        <v>37.77855240414913</v>
+        <v>46.08983393306194</v>
       </c>
       <c r="F603">
-        <v>11.89719447099302</v>
+        <v>14.51457725461149</v>
       </c>
       <c r="G603">
-        <v>62.1314909287503</v>
+        <v>75.80041893307536</v>
       </c>
     </row>
     <row r="604">
@@ -16825,13 +16825,13 @@
         </is>
       </c>
       <c r="E610">
-        <v>41.68087080637491</v>
+        <v>49.56047005775674</v>
       </c>
       <c r="F610">
-        <v>17.87324375432772</v>
+        <v>21.25210785629427</v>
       </c>
       <c r="G610">
-        <v>65.8309833389519</v>
+        <v>78.27606322811771</v>
       </c>
     </row>
     <row r="611">
@@ -16852,13 +16852,13 @@
         </is>
       </c>
       <c r="E611">
-        <v>37.97455252945106</v>
+        <v>45.64816677115361</v>
       </c>
       <c r="F611">
-        <v>11.60438393152563</v>
+        <v>13.94931125447641</v>
       </c>
       <c r="G611">
-        <v>63.28791576546828</v>
+        <v>76.07666558336084</v>
       </c>
     </row>
     <row r="612">
@@ -17041,13 +17041,13 @@
         </is>
       </c>
       <c r="E618">
-        <v>58.59925788365919</v>
+        <v>72.015631549785</v>
       </c>
       <c r="F618">
-        <v>30.61119813149644</v>
+        <v>37.61967037726002</v>
       </c>
       <c r="G618">
-        <v>88.49138299870222</v>
+        <v>108.7515962406503</v>
       </c>
     </row>
     <row r="619">
@@ -17068,13 +17068,13 @@
         </is>
       </c>
       <c r="E619">
-        <v>42.23374898622517</v>
+        <v>52.98415781908249</v>
       </c>
       <c r="F619">
-        <v>14.54212936006808</v>
+        <v>18.2437622880854</v>
       </c>
       <c r="G619">
-        <v>69.79213587735067</v>
+        <v>87.55740682794902</v>
       </c>
     </row>
     <row r="620">
@@ -17257,13 +17257,13 @@
         </is>
       </c>
       <c r="E626">
-        <v>65.7968686872707</v>
+        <v>81.16152208951799</v>
       </c>
       <c r="F626">
-        <v>33.45206715374967</v>
+        <v>41.26367624185056</v>
       </c>
       <c r="G626">
-        <v>98.34048960681154</v>
+        <v>121.3046149270835</v>
       </c>
     </row>
     <row r="627">
@@ -17284,13 +17284,13 @@
         </is>
       </c>
       <c r="E627">
-        <v>43.63096081223282</v>
+        <v>54.2963067885564</v>
       </c>
       <c r="F627">
-        <v>14.42292658159311</v>
+        <v>17.94853085709364</v>
       </c>
       <c r="G627">
-        <v>71.97490906866619</v>
+        <v>89.56877572989572</v>
       </c>
     </row>
     <row r="628">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="E634">
-        <v>-2.456335783538781</v>
+        <v>-2.854028243730774</v>
       </c>
       <c r="F634">
-        <v>-4.882023701950502</v>
+        <v>-5.672446587028202</v>
       </c>
       <c r="G634">
-        <v>-0.5050682301620858</v>
+        <v>-0.5868411817121378</v>
       </c>
     </row>
     <row r="635">
@@ -17500,13 +17500,13 @@
         </is>
       </c>
       <c r="E635">
-        <v>-1.86436685013408</v>
+        <v>-2.512842276267673</v>
       </c>
       <c r="F635">
-        <v>-2.997587327572591</v>
+        <v>-4.040226398032622</v>
       </c>
       <c r="G635">
-        <v>-0.669254241464649</v>
+        <v>-0.902038325452353</v>
       </c>
     </row>
     <row r="636">
@@ -17689,13 +17689,13 @@
         </is>
       </c>
       <c r="E642">
-        <v>-2.085103504222027</v>
+        <v>-2.52315045889052</v>
       </c>
       <c r="F642">
-        <v>-4.917756909706475</v>
+        <v>-5.950899117628003</v>
       </c>
       <c r="G642">
-        <v>0.2247903679339378</v>
+        <v>0.27201523514695</v>
       </c>
     </row>
     <row r="643">
@@ -17716,13 +17716,13 @@
         </is>
       </c>
       <c r="E643">
-        <v>-2.795347931621131</v>
+        <v>-3.522138393842626</v>
       </c>
       <c r="F643">
-        <v>-4.538721676097814</v>
+        <v>-5.718789311883246</v>
       </c>
       <c r="G643">
-        <v>-0.9659971996606268</v>
+        <v>-1.21715647157239</v>
       </c>
     </row>
     <row r="644">
@@ -17905,13 +17905,13 @@
         </is>
       </c>
       <c r="E650">
-        <v>-3.106798721577304</v>
+        <v>-3.745579767135254</v>
       </c>
       <c r="F650">
-        <v>-6.005596198683056</v>
+        <v>-7.240391678786115</v>
       </c>
       <c r="G650">
-        <v>-0.8200328735609806</v>
+        <v>-0.9886377634520234</v>
       </c>
     </row>
     <row r="651">
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="E651">
-        <v>-3.291329609227517</v>
+        <v>-3.847610669942027</v>
       </c>
       <c r="F651">
-        <v>-5.615776893613617</v>
+        <v>-6.564922284083524</v>
       </c>
       <c r="G651">
-        <v>-1.17926134756368</v>
+        <v>-1.378573124616697</v>
       </c>
     </row>
     <row r="652">
@@ -18121,13 +18121,13 @@
         </is>
       </c>
       <c r="E658">
-        <v>-2.805329047545181</v>
+        <v>-3.359870836013414</v>
       </c>
       <c r="F658">
-        <v>-5.211673382337236</v>
+        <v>-6.241887888148085</v>
       </c>
       <c r="G658">
-        <v>-0.826624992263288</v>
+        <v>-0.9900276070130077</v>
       </c>
     </row>
     <row r="659">
@@ -18148,13 +18148,13 @@
         </is>
       </c>
       <c r="E659">
-        <v>-1.519598363097335</v>
+        <v>-1.921001704292857</v>
       </c>
       <c r="F659">
-        <v>-2.620397622819679</v>
+        <v>-3.312578126960726</v>
       </c>
       <c r="G659">
-        <v>-0.5475039928194745</v>
+        <v>-0.6921276890359395</v>
       </c>
     </row>
     <row r="660">
@@ -18337,13 +18337,13 @@
         </is>
       </c>
       <c r="E666">
-        <v>-1.722160643870449</v>
+        <v>-2.136141567877768</v>
       </c>
       <c r="F666">
-        <v>-3.985405603939243</v>
+        <v>-4.943435797193868</v>
       </c>
       <c r="G666">
-        <v>0.1757109467233595</v>
+        <v>0.217949155070321</v>
       </c>
     </row>
     <row r="667">
@@ -18364,13 +18364,13 @@
         </is>
       </c>
       <c r="E667">
-        <v>-2.299692131489824</v>
+        <v>-2.70552015469391</v>
       </c>
       <c r="F667">
-        <v>-3.836172753721238</v>
+        <v>-4.513144416142633</v>
       </c>
       <c r="G667">
-        <v>-0.8255646322273369</v>
+        <v>-0.9712525085027492</v>
       </c>
     </row>
     <row r="668">
@@ -18553,13 +18553,13 @@
         </is>
       </c>
       <c r="E674">
-        <v>-1.220592008914433</v>
+        <v>-1.549621159143541</v>
       </c>
       <c r="F674">
-        <v>-3.000947469104033</v>
+        <v>-3.809898525992946</v>
       </c>
       <c r="G674">
-        <v>0.4163065105537039</v>
+        <v>0.5285282655725285</v>
       </c>
     </row>
     <row r="675">
@@ -18580,13 +18580,13 @@
         </is>
       </c>
       <c r="E675">
-        <v>-1.570235497482554</v>
+        <v>-2.001280536007177</v>
       </c>
       <c r="F675">
-        <v>-2.49971724827848</v>
+        <v>-3.185914139962769</v>
       </c>
       <c r="G675">
-        <v>-0.558875632836272</v>
+        <v>-0.7122924732226995</v>
       </c>
     </row>
     <row r="676">
@@ -18769,13 +18769,13 @@
         </is>
       </c>
       <c r="E682">
-        <v>-1.469656482360396</v>
+        <v>-1.909038317292886</v>
       </c>
       <c r="F682">
-        <v>-3.05821529087553</v>
+        <v>-3.972527078869244</v>
       </c>
       <c r="G682">
-        <v>-0.1673014569885601</v>
+        <v>-0.217319418356274</v>
       </c>
     </row>
     <row r="683">
@@ -18796,13 +18796,13 @@
         </is>
       </c>
       <c r="E683">
-        <v>-0.823669634647726</v>
+        <v>-1.016443378926981</v>
       </c>
       <c r="F683">
-        <v>-1.24804393814319</v>
+        <v>-1.540139327921383</v>
       </c>
       <c r="G683">
-        <v>-0.09290236935827906</v>
+        <v>-0.1146454770804295</v>
       </c>
     </row>
     <row r="684">
@@ -18904,13 +18904,13 @@
         </is>
       </c>
       <c r="E687">
-        <v>2.125628740044517</v>
+        <v>2.732951237200093</v>
       </c>
       <c r="F687">
-        <v>0.02661423677825917</v>
+        <v>0.03421830442919036</v>
       </c>
       <c r="G687">
-        <v>4.593375534081073</v>
+        <v>5.905768543818521</v>
       </c>
     </row>
     <row r="688">
@@ -18931,13 +18931,13 @@
         </is>
       </c>
       <c r="E688">
-        <v>0.08171408745960274</v>
+        <v>0.1634281749192055</v>
       </c>
       <c r="F688">
-        <v>-0.08760682102264285</v>
+        <v>-0.1752136420452857</v>
       </c>
       <c r="G688">
-        <v>0.2811143884627791</v>
+        <v>0.5622287769255583</v>
       </c>
     </row>
     <row r="689">
@@ -19066,13 +19066,13 @@
         </is>
       </c>
       <c r="E693">
-        <v>2.754452734976387</v>
+        <v>4.223494193630459</v>
       </c>
       <c r="F693">
-        <v>0.487695402527393</v>
+        <v>0.7477996172086693</v>
       </c>
       <c r="G693">
-        <v>5.223597170868016</v>
+        <v>8.009515661997625</v>
       </c>
     </row>
     <row r="694">
@@ -19201,13 +19201,13 @@
         </is>
       </c>
       <c r="E698">
-        <v>0.6028333940902831</v>
+        <v>0.9042500911354248</v>
       </c>
       <c r="F698">
-        <v>-0.1737510648197239</v>
+        <v>-0.2606265972295858</v>
       </c>
       <c r="G698">
-        <v>1.435724002682951</v>
+        <v>2.153586004024427</v>
       </c>
     </row>
     <row r="699">
@@ -19336,13 +19336,13 @@
         </is>
       </c>
       <c r="E703">
-        <v>1.904741635770037</v>
+        <v>2.490815985237741</v>
       </c>
       <c r="F703">
-        <v>-0.5654199329490892</v>
+        <v>-0.7393952969334243</v>
       </c>
       <c r="G703">
-        <v>4.59668691657606</v>
+        <v>6.011052121676387</v>
       </c>
     </row>
     <row r="704">
@@ -19363,13 +19363,13 @@
         </is>
       </c>
       <c r="E704">
-        <v>0.09688872284463772</v>
+        <v>0.1937774456892754</v>
       </c>
       <c r="F704">
-        <v>-0.1421691886120818</v>
+        <v>-0.2843383772241636</v>
       </c>
       <c r="G704">
-        <v>0.3385907508142578</v>
+        <v>0.6771815016285156</v>
       </c>
     </row>
     <row r="705">
@@ -19471,13 +19471,13 @@
         </is>
       </c>
       <c r="E708">
-        <v>2.69015305811934</v>
+        <v>3.407527206951165</v>
       </c>
       <c r="F708">
-        <v>-0.1002832456484135</v>
+        <v>-0.1270254444879904</v>
       </c>
       <c r="G708">
-        <v>5.597412525781812</v>
+        <v>7.090055865990296</v>
       </c>
     </row>
     <row r="709">
@@ -19633,13 +19633,13 @@
         </is>
       </c>
       <c r="E714">
-        <v>4.097458528504307</v>
+        <v>4.631909640917912</v>
       </c>
       <c r="F714">
-        <v>-0.5268075989358973</v>
+        <v>-0.5955216335797101</v>
       </c>
       <c r="G714">
-        <v>8.88522537529407</v>
+        <v>10.04416781554982</v>
       </c>
     </row>
     <row r="715">
@@ -19741,13 +19741,13 @@
         </is>
       </c>
       <c r="E718">
-        <v>2.429564555814908</v>
+        <v>2.75350649659023</v>
       </c>
       <c r="F718">
-        <v>-0.8717774954825082</v>
+        <v>-0.9880144948801759</v>
       </c>
       <c r="G718">
-        <v>5.765368788726493</v>
+        <v>6.534084627223358</v>
       </c>
     </row>
     <row r="719">
@@ -19768,13 +19768,13 @@
         </is>
       </c>
       <c r="E719">
-        <v>0.1026387783081463</v>
+        <v>0.2052775566162925</v>
       </c>
       <c r="F719">
-        <v>-0.1360024978643408</v>
+        <v>-0.2720049957286817</v>
       </c>
       <c r="G719">
-        <v>0.3474573171289826</v>
+        <v>0.6949146342579653</v>
       </c>
     </row>
     <row r="720">
@@ -19930,13 +19930,13 @@
         </is>
       </c>
       <c r="E725">
-        <v>27.08320197673871</v>
+        <v>36.93163905918915</v>
       </c>
       <c r="F725">
-        <v>11.32877516175503</v>
+        <v>15.44832976602959</v>
       </c>
       <c r="G725">
-        <v>43.09819247571166</v>
+        <v>58.77026246687953</v>
       </c>
     </row>
     <row r="726">
@@ -19957,13 +19957,13 @@
         </is>
       </c>
       <c r="E726">
-        <v>15.82772815948927</v>
+        <v>21.58326567203082</v>
       </c>
       <c r="F726">
-        <v>7.120390074383808</v>
+        <v>9.709622828705193</v>
       </c>
       <c r="G726">
-        <v>24.01798912716435</v>
+        <v>32.75180335522411</v>
       </c>
     </row>
     <row r="727">
@@ -20146,13 +20146,13 @@
         </is>
       </c>
       <c r="E733">
-        <v>24.4141311281712</v>
+        <v>29.48719733662235</v>
       </c>
       <c r="F733">
-        <v>10.17307167833181</v>
+        <v>12.28695670240075</v>
       </c>
       <c r="G733">
-        <v>37.90318914274584</v>
+        <v>45.77917649708264</v>
       </c>
     </row>
     <row r="734">
@@ -20173,13 +20173,13 @@
         </is>
       </c>
       <c r="E734">
-        <v>22.22772810494061</v>
+        <v>26.74862195679294</v>
       </c>
       <c r="F734">
-        <v>10.04803521670989</v>
+        <v>12.0917033963797</v>
       </c>
       <c r="G734">
-        <v>33.49720704777022</v>
+        <v>40.31019831172349</v>
       </c>
     </row>
     <row r="735">
@@ -20362,13 +20362,13 @@
         </is>
       </c>
       <c r="E741">
-        <v>26.30629788557368</v>
+        <v>32.26905873963705</v>
       </c>
       <c r="F741">
-        <v>10.57755190769419</v>
+        <v>12.97513034010488</v>
       </c>
       <c r="G741">
-        <v>40.49347289505658</v>
+        <v>49.67199341793608</v>
       </c>
     </row>
     <row r="742">
@@ -20389,13 +20389,13 @@
         </is>
       </c>
       <c r="E742">
-        <v>19.75080572905309</v>
+        <v>27.73517400250008</v>
       </c>
       <c r="F742">
-        <v>9.370266450719368</v>
+        <v>13.1582465052655</v>
       </c>
       <c r="G742">
-        <v>28.49282151020951</v>
+        <v>40.01119616327293</v>
       </c>
     </row>
     <row r="743">
@@ -20578,13 +20578,13 @@
         </is>
       </c>
       <c r="E749">
-        <v>27.93700336681844</v>
+        <v>34.4901276133561</v>
       </c>
       <c r="F749">
-        <v>10.99613246619287</v>
+        <v>13.57547218048502</v>
       </c>
       <c r="G749">
-        <v>43.27886005776575</v>
+        <v>53.43069142934043</v>
       </c>
     </row>
     <row r="750">
@@ -20605,13 +20605,13 @@
         </is>
       </c>
       <c r="E750">
-        <v>27.67906929729093</v>
+        <v>34.16635116384349</v>
       </c>
       <c r="F750">
-        <v>13.13099709070669</v>
+        <v>16.20857453384107</v>
       </c>
       <c r="G750">
-        <v>39.56696510109136</v>
+        <v>48.84047254665964</v>
       </c>
     </row>
     <row r="751">
@@ -20794,13 +20794,13 @@
         </is>
       </c>
       <c r="E757">
-        <v>32.54901998353177</v>
+        <v>42.80903715225374</v>
       </c>
       <c r="F757">
-        <v>13.69074891447008</v>
+        <v>18.00631107229217</v>
       </c>
       <c r="G757">
-        <v>49.31159104886876</v>
+        <v>64.85546214035999</v>
       </c>
     </row>
     <row r="758">
@@ -20821,13 +20821,13 @@
         </is>
       </c>
       <c r="E758">
-        <v>26.57635486731197</v>
+        <v>31.53126848664131</v>
       </c>
       <c r="F758">
-        <v>13.42072940871665</v>
+        <v>15.92289929847738</v>
       </c>
       <c r="G758">
-        <v>37.36823189253733</v>
+        <v>44.33519038097649</v>
       </c>
     </row>
     <row r="759">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="E765">
-        <v>33.36609992912709</v>
+        <v>42.26372657689431</v>
       </c>
       <c r="F765">
-        <v>14.28246768974081</v>
+        <v>18.09112574033836</v>
       </c>
       <c r="G765">
-        <v>50.35897097581319</v>
+        <v>63.78802990269671</v>
       </c>
     </row>
     <row r="766">
@@ -21037,13 +21037,13 @@
         </is>
       </c>
       <c r="E766">
-        <v>24.96600640621872</v>
+        <v>34.16400876640456</v>
       </c>
       <c r="F766">
-        <v>12.53123591102502</v>
+        <v>17.14800703613951</v>
       </c>
       <c r="G766">
-        <v>35.35837290011658</v>
+        <v>48.38514186331743</v>
       </c>
     </row>
     <row r="767">
@@ -21199,13 +21199,13 @@
         </is>
       </c>
       <c r="E772">
-        <v>42.19161037710333</v>
+        <v>52.83453912087714</v>
       </c>
       <c r="F772">
-        <v>17.14288681721244</v>
+        <v>21.46721862695973</v>
       </c>
       <c r="G772">
-        <v>63.22188097792023</v>
+        <v>79.16974284622444</v>
       </c>
     </row>
     <row r="773">
@@ -21226,13 +21226,13 @@
         </is>
       </c>
       <c r="E773">
-        <v>37.11261326359438</v>
+        <v>43.22527897759816</v>
       </c>
       <c r="F773">
-        <v>17.7175713823193</v>
+        <v>20.63575960999542</v>
       </c>
       <c r="G773">
-        <v>53.01436892824759</v>
+        <v>61.74614733995895</v>
       </c>
     </row>
     <row r="774">
@@ -21415,13 +21415,13 @@
         </is>
       </c>
       <c r="E780">
-        <v>141.6547709698381</v>
+        <v>168.046724496538</v>
       </c>
       <c r="F780">
-        <v>88.17067314537005</v>
+        <v>104.5979088264466</v>
       </c>
       <c r="G780">
-        <v>191.978088042474</v>
+        <v>227.7458687043798</v>
       </c>
     </row>
     <row r="781">
@@ -21442,13 +21442,13 @@
         </is>
       </c>
       <c r="E781">
-        <v>37.94892348466836</v>
+        <v>46.78634402219387</v>
       </c>
       <c r="F781">
-        <v>22.29900490049976</v>
+        <v>27.49192384993121</v>
       </c>
       <c r="G781">
-        <v>52.66556654939539</v>
+        <v>64.93015054035048</v>
       </c>
     </row>
     <row r="782">
@@ -21631,13 +21631,13 @@
         </is>
       </c>
       <c r="E788">
-        <v>165.8431651234697</v>
+        <v>194.6598853044981</v>
       </c>
       <c r="F788">
-        <v>113.9288538962224</v>
+        <v>133.7250022682611</v>
       </c>
       <c r="G788">
-        <v>210.9039308729775</v>
+        <v>247.5503585778566</v>
       </c>
     </row>
     <row r="789">
@@ -21658,13 +21658,13 @@
         </is>
       </c>
       <c r="E789">
-        <v>33.65219940997081</v>
+        <v>40.49671454420216</v>
       </c>
       <c r="F789">
-        <v>22.88694309586152</v>
+        <v>27.5419145729859</v>
       </c>
       <c r="G789">
-        <v>44.14764561082224</v>
+        <v>53.12682776895558</v>
       </c>
     </row>
     <row r="790">
@@ -21847,13 +21847,13 @@
         </is>
       </c>
       <c r="E796">
-        <v>155.1329749588934</v>
+        <v>190.2890088524555</v>
       </c>
       <c r="F796">
-        <v>86.47982377657976</v>
+        <v>106.0777694525673</v>
       </c>
       <c r="G796">
-        <v>211.5053346873893</v>
+        <v>259.4363997424452</v>
       </c>
     </row>
     <row r="797">
@@ -21874,13 +21874,13 @@
         </is>
       </c>
       <c r="E797">
-        <v>36.54272709406871</v>
+        <v>46.82036908927553</v>
       </c>
       <c r="F797">
-        <v>21.69755829605271</v>
+        <v>27.79999656681754</v>
       </c>
       <c r="G797">
-        <v>48.89035877266971</v>
+        <v>62.64077217748307</v>
       </c>
     </row>
     <row r="798">
@@ -22063,13 +22063,13 @@
         </is>
       </c>
       <c r="E804">
-        <v>138.2065443318018</v>
+        <v>160.2314916356746</v>
       </c>
       <c r="F804">
-        <v>76.73117347430028</v>
+        <v>88.95924892837205</v>
       </c>
       <c r="G804">
-        <v>189.8434721549938</v>
+        <v>220.0974119406502</v>
       </c>
     </row>
     <row r="805">
@@ -22090,13 +22090,13 @@
         </is>
       </c>
       <c r="E805">
-        <v>40.01235213237144</v>
+        <v>49.72963765023307</v>
       </c>
       <c r="F805">
-        <v>22.45240420128614</v>
+        <v>27.90513093588421</v>
       </c>
       <c r="G805">
-        <v>53.88132377025397</v>
+        <v>66.96678811445851</v>
       </c>
     </row>
     <row r="806">
@@ -22252,13 +22252,13 @@
         </is>
       </c>
       <c r="E811">
-        <v>180.9056298059163</v>
+        <v>205.0656650568692</v>
       </c>
       <c r="F811">
-        <v>114.9292151452806</v>
+        <v>130.2780679822725</v>
       </c>
       <c r="G811">
-        <v>235.310930879466</v>
+        <v>266.7368206711863</v>
       </c>
     </row>
     <row r="812">
@@ -22279,13 +22279,13 @@
         </is>
       </c>
       <c r="E812">
-        <v>48.81562554199855</v>
+        <v>54.23958393555395</v>
       </c>
       <c r="F812">
-        <v>30.50239974684381</v>
+        <v>33.8915552742709</v>
       </c>
       <c r="G812">
-        <v>63.6217460305926</v>
+        <v>70.69082892288067</v>
       </c>
     </row>
     <row r="813">
@@ -22468,13 +22468,13 @@
         </is>
       </c>
       <c r="E819">
-        <v>218.1190711125994</v>
+        <v>273.8742269307077</v>
       </c>
       <c r="F819">
-        <v>141.6943505568777</v>
+        <v>177.9139738733829</v>
       </c>
       <c r="G819">
-        <v>279.0751533504737</v>
+        <v>350.4117796282633</v>
       </c>
     </row>
     <row r="820">
@@ -22495,13 +22495,13 @@
         </is>
       </c>
       <c r="E820">
-        <v>44.85511272391225</v>
+        <v>54.75818955906171</v>
       </c>
       <c r="F820">
-        <v>26.95595931057846</v>
+        <v>32.90727500252435</v>
       </c>
       <c r="G820">
-        <v>59.48782075033842</v>
+        <v>72.6214954614521</v>
       </c>
     </row>
     <row r="821">
@@ -22684,13 +22684,13 @@
         </is>
       </c>
       <c r="E827">
-        <v>144.1716411528298</v>
+        <v>172.5233864841395</v>
       </c>
       <c r="F827">
-        <v>88.68230288234631</v>
+        <v>106.1219189303391</v>
       </c>
       <c r="G827">
-        <v>188.0192442271105</v>
+        <v>224.9937399537808</v>
       </c>
     </row>
     <row r="828">
@@ -22711,13 +22711,13 @@
         </is>
       </c>
       <c r="E828">
-        <v>45.1615159518471</v>
+        <v>54.4254166599183</v>
       </c>
       <c r="F828">
-        <v>25.74066074701791</v>
+        <v>31.02079628486774</v>
       </c>
       <c r="G828">
-        <v>60.51891284616734</v>
+        <v>72.93304881461192</v>
       </c>
     </row>
     <row r="829">
@@ -22900,13 +22900,13 @@
         </is>
       </c>
       <c r="E835">
-        <v>1.48979954060116</v>
+        <v>1.910829845553662</v>
       </c>
       <c r="F835">
-        <v>0.2797324178975112</v>
+        <v>0.3587872316511556</v>
       </c>
       <c r="G835">
-        <v>2.945510619412209</v>
+        <v>3.77793753359392</v>
       </c>
     </row>
     <row r="836">
@@ -22927,13 +22927,13 @@
         </is>
       </c>
       <c r="E836">
-        <v>0.2539025228297414</v>
+        <v>0.3151893386851962</v>
       </c>
       <c r="F836">
-        <v>0.04867393992716267</v>
+        <v>0.06042282197854676</v>
       </c>
       <c r="G836">
-        <v>0.4997630369133993</v>
+        <v>0.6203954940993922</v>
       </c>
     </row>
     <row r="837">
@@ -23116,13 +23116,13 @@
         </is>
       </c>
       <c r="E843">
-        <v>3.47988234094253</v>
+        <v>4.21022801743664</v>
       </c>
       <c r="F843">
-        <v>0.664244765166135</v>
+        <v>0.8036541603244596</v>
       </c>
       <c r="G843">
-        <v>6.903262656526572</v>
+        <v>8.352095559748198</v>
       </c>
     </row>
     <row r="844">
@@ -23143,13 +23143,13 @@
         </is>
       </c>
       <c r="E844">
-        <v>0.5820033602435781</v>
+        <v>0.6790039202841744</v>
       </c>
       <c r="F844">
-        <v>0.1096449258019781</v>
+        <v>0.1279190801023077</v>
       </c>
       <c r="G844">
-        <v>1.140362376914048</v>
+        <v>1.330422773066389</v>
       </c>
     </row>
     <row r="845">
@@ -23332,13 +23332,13 @@
         </is>
       </c>
       <c r="E851">
-        <v>2.633261262358169</v>
+        <v>3.234331767896446</v>
       </c>
       <c r="F851">
-        <v>0.5335191825926133</v>
+        <v>0.6553007351409272</v>
       </c>
       <c r="G851">
-        <v>5.157691477781404</v>
+        <v>6.334990619448898</v>
       </c>
     </row>
     <row r="852">
@@ -23359,13 +23359,13 @@
         </is>
       </c>
       <c r="E852">
-        <v>0.4213660121712154</v>
+        <v>0.5038071884655837</v>
       </c>
       <c r="F852">
-        <v>0.08868772360895466</v>
+        <v>0.1060396695324458</v>
       </c>
       <c r="G852">
-        <v>0.8051637888408976</v>
+        <v>0.9626958344836819</v>
       </c>
     </row>
     <row r="853">
@@ -23548,13 +23548,13 @@
         </is>
       </c>
       <c r="E859">
-        <v>2.486423824095212</v>
+        <v>3.094216314429597</v>
       </c>
       <c r="F859">
-        <v>0.4934808345016909</v>
+        <v>0.6141094829354375</v>
       </c>
       <c r="G859">
-        <v>4.842089170954975</v>
+        <v>6.025710968299524</v>
       </c>
     </row>
     <row r="860">
@@ -23575,13 +23575,13 @@
         </is>
       </c>
       <c r="E860">
-        <v>0.4108104511587232</v>
+        <v>0.5396921613261657</v>
       </c>
       <c r="F860">
-        <v>0.07671369281472394</v>
+        <v>0.1007807336977746</v>
       </c>
       <c r="G860">
-        <v>0.830663341781533</v>
+        <v>1.091263605869857</v>
       </c>
     </row>
     <row r="861">
@@ -23764,13 +23764,13 @@
         </is>
       </c>
       <c r="E867">
-        <v>3.58167894290988</v>
+        <v>4.554961264352782</v>
       </c>
       <c r="F867">
-        <v>0.7238918476159032</v>
+        <v>0.9206015888158769</v>
       </c>
       <c r="G867">
-        <v>7.167235335389561</v>
+        <v>9.114853633049767</v>
       </c>
     </row>
     <row r="868">
@@ -23791,13 +23791,13 @@
         </is>
       </c>
       <c r="E868">
-        <v>0.4933574548131283</v>
+        <v>0.6503348267991237</v>
       </c>
       <c r="F868">
-        <v>0.09709200229583786</v>
+        <v>0.1279849121172408</v>
       </c>
       <c r="G868">
-        <v>0.9977666465859637</v>
+        <v>1.315237852317861</v>
       </c>
     </row>
     <row r="869">
@@ -23980,13 +23980,13 @@
         </is>
       </c>
       <c r="E875">
-        <v>2.605802387086932</v>
+        <v>3.212633079970189</v>
       </c>
       <c r="F875">
-        <v>0.4899296779228449</v>
+        <v>0.6040228905898087</v>
       </c>
       <c r="G875">
-        <v>5.191923148887527</v>
+        <v>6.401001142464075</v>
       </c>
     </row>
     <row r="876">
@@ -24007,13 +24007,13 @@
         </is>
       </c>
       <c r="E876">
-        <v>0.3598366328871679</v>
+        <v>0.4924080239508614</v>
       </c>
       <c r="F876">
-        <v>0.06860570124772224</v>
+        <v>0.09388148591793569</v>
       </c>
       <c r="G876">
-        <v>0.7008446779000597</v>
+        <v>0.9590506118632396</v>
       </c>
     </row>
     <row r="877">
@@ -24196,13 +24196,13 @@
         </is>
       </c>
       <c r="E883">
-        <v>3.889189748688253</v>
+        <v>5.204650987215161</v>
       </c>
       <c r="F883">
-        <v>0.7191645355029908</v>
+        <v>0.9624113636878259</v>
       </c>
       <c r="G883">
-        <v>7.758243292404146</v>
+        <v>10.38235499424672</v>
       </c>
     </row>
     <row r="884">
@@ -24223,13 +24223,13 @@
         </is>
       </c>
       <c r="E884">
-        <v>0.7854653777765308</v>
+        <v>0.9660321312883771</v>
       </c>
       <c r="F884">
-        <v>0.1528095878181605</v>
+        <v>0.1879382286958985</v>
       </c>
       <c r="G884">
-        <v>1.596377331537025</v>
+        <v>1.963360626143237</v>
       </c>
     </row>
     <row r="885">
@@ -24358,13 +24358,13 @@
         </is>
       </c>
       <c r="E889">
-        <v>4.417788938692337</v>
+        <v>5.842882144722123</v>
       </c>
       <c r="F889">
-        <v>0.4585544231782574</v>
+        <v>0.606475204848663</v>
       </c>
       <c r="G889">
-        <v>9.005637728920384</v>
+        <v>11.91068215760438</v>
       </c>
     </row>
     <row r="890">
@@ -24385,13 +24385,13 @@
         </is>
       </c>
       <c r="E890">
-        <v>0.5201740329886118</v>
+        <v>0.6687951852710723</v>
       </c>
       <c r="F890">
-        <v>-0.4827239225065672</v>
+        <v>-0.6206450432227293</v>
       </c>
       <c r="G890">
-        <v>1.689497487738803</v>
+        <v>2.172211055664175</v>
       </c>
     </row>
     <row r="891">
@@ -24520,13 +24520,13 @@
         </is>
       </c>
       <c r="E895">
-        <v>5.768997876337388</v>
+        <v>7.342360933520312</v>
       </c>
       <c r="F895">
-        <v>1.531364815778941</v>
+        <v>1.949009765536834</v>
       </c>
       <c r="G895">
-        <v>10.29415854201336</v>
+        <v>13.10165632619883</v>
       </c>
     </row>
     <row r="896">
@@ -24547,13 +24547,13 @@
         </is>
       </c>
       <c r="E896">
-        <v>1.365699135583196</v>
+        <v>1.729885571738714</v>
       </c>
       <c r="F896">
-        <v>-0.9216420130036517</v>
+        <v>-1.167413216471292</v>
       </c>
       <c r="G896">
-        <v>3.980063542361834</v>
+        <v>5.041413820324989</v>
       </c>
     </row>
     <row r="897">
@@ -24682,13 +24682,13 @@
         </is>
       </c>
       <c r="E901">
-        <v>4.625095107469426</v>
+        <v>5.606175887841729</v>
       </c>
       <c r="F901">
-        <v>-0.8368863110535227</v>
+        <v>-1.014407649761846</v>
       </c>
       <c r="G901">
-        <v>10.46205816082085</v>
+        <v>12.68128261917678</v>
       </c>
     </row>
     <row r="902">
@@ -24709,13 +24709,13 @@
         </is>
       </c>
       <c r="E902">
-        <v>1.829735803341303</v>
+        <v>2.09112663239006</v>
       </c>
       <c r="F902">
-        <v>-2.17007348501242</v>
+        <v>-2.480083982871337</v>
       </c>
       <c r="G902">
-        <v>5.942212264830601</v>
+        <v>6.791099731234972</v>
       </c>
     </row>
     <row r="903">
@@ -24844,13 +24844,13 @@
         </is>
       </c>
       <c r="E907">
-        <v>5.581800920476157</v>
+        <v>6.807074293263605</v>
       </c>
       <c r="F907">
-        <v>-1.090181297080979</v>
+        <v>-1.32948938668412</v>
       </c>
       <c r="G907">
-        <v>12.77730771332073</v>
+        <v>15.5820825772204</v>
       </c>
     </row>
     <row r="908">
@@ -24871,13 +24871,13 @@
         </is>
       </c>
       <c r="E908">
-        <v>1.227637166054055</v>
+        <v>1.5783906420695</v>
       </c>
       <c r="F908">
-        <v>-1.626671235478461</v>
+        <v>-2.091434445615164</v>
       </c>
       <c r="G908">
-        <v>4.110930028139825</v>
+        <v>5.285481464751205</v>
       </c>
     </row>
     <row r="909">
@@ -25006,13 +25006,13 @@
         </is>
       </c>
       <c r="E913">
-        <v>5.399202929563691</v>
+        <v>6.749003661954614</v>
       </c>
       <c r="F913">
-        <v>0.3372701968313596</v>
+        <v>0.4215877460391995</v>
       </c>
       <c r="G913">
-        <v>10.62126674664567</v>
+        <v>13.27658343330708</v>
       </c>
     </row>
     <row r="914">
@@ -25033,13 +25033,13 @@
         </is>
       </c>
       <c r="E914">
-        <v>1.611635646440714</v>
+        <v>1.712362874343259</v>
       </c>
       <c r="F914">
-        <v>-1.759045395501665</v>
+        <v>-1.868985732720519</v>
       </c>
       <c r="G914">
-        <v>4.949992544911482</v>
+        <v>5.25936707896845</v>
       </c>
     </row>
     <row r="915">
@@ -25195,13 +25195,13 @@
         </is>
       </c>
       <c r="E920">
-        <v>5.402126043374929</v>
+        <v>7.934372626206926</v>
       </c>
       <c r="F920">
-        <v>-0.09944820071460393</v>
+        <v>-0.1460645447995745</v>
       </c>
       <c r="G920">
-        <v>11.03454703169396</v>
+        <v>16.2069909528005</v>
       </c>
     </row>
     <row r="921">
@@ -25222,13 +25222,13 @@
         </is>
       </c>
       <c r="E921">
-        <v>1.309297510128935</v>
+        <v>1.58986126229942</v>
       </c>
       <c r="F921">
-        <v>-1.49261091003931</v>
+        <v>-1.812456105047734</v>
       </c>
       <c r="G921">
-        <v>4.152765337914405</v>
+        <v>5.042643624610349</v>
       </c>
     </row>
     <row r="922">
@@ -25357,13 +25357,13 @@
         </is>
       </c>
       <c r="E926">
-        <v>5.33860600133973</v>
+        <v>6.253795601569397</v>
       </c>
       <c r="F926">
-        <v>-1.239073081002079</v>
+        <v>-1.451485609173864</v>
       </c>
       <c r="G926">
-        <v>11.95904672995282</v>
+        <v>14.00916902651617</v>
       </c>
     </row>
     <row r="927">
@@ -25384,13 +25384,13 @@
         </is>
       </c>
       <c r="E927">
-        <v>0.9395446425744157</v>
+        <v>1.315362499604182</v>
       </c>
       <c r="F927">
-        <v>-1.091229638175931</v>
+        <v>-1.527721493446304</v>
       </c>
       <c r="G927">
-        <v>3.026869503197889</v>
+        <v>4.237617304477045</v>
       </c>
     </row>
     <row r="928">
@@ -25546,13 +25546,13 @@
         </is>
       </c>
       <c r="E933">
-        <v>3.391665127615793</v>
+        <v>3.633926922445492</v>
       </c>
       <c r="F933">
-        <v>1.350565923902481</v>
+        <v>1.447034918466944</v>
       </c>
       <c r="G933">
-        <v>5.773632731179529</v>
+        <v>6.186035069120924</v>
       </c>
     </row>
     <row r="934">
@@ -25573,13 +25573,13 @@
         </is>
       </c>
       <c r="E934">
-        <v>0.1103045893329295</v>
+        <v>0.2206091786658591</v>
       </c>
       <c r="F934">
-        <v>-0.07275146799256313</v>
+        <v>-0.1455029359851263</v>
       </c>
       <c r="G934">
-        <v>0.3293568606663007</v>
+        <v>0.6587137213326013</v>
       </c>
     </row>
     <row r="935">
@@ -25735,13 +25735,13 @@
         </is>
       </c>
       <c r="E940">
-        <v>4.232654556813756</v>
+        <v>5.744316898532955</v>
       </c>
       <c r="F940">
-        <v>2.229177837769312</v>
+        <v>3.02531277982978</v>
       </c>
       <c r="G940">
-        <v>6.294156175334476</v>
+        <v>8.542069095096789</v>
       </c>
     </row>
     <row r="941">
@@ -25951,13 +25951,13 @@
         </is>
       </c>
       <c r="E948">
-        <v>4.095113421941668</v>
+        <v>5.687657530474539</v>
       </c>
       <c r="F948">
-        <v>0.6595559430971364</v>
+        <v>0.9160499209682449</v>
       </c>
       <c r="G948">
-        <v>7.790145004982247</v>
+        <v>10.81964584025312</v>
       </c>
     </row>
     <row r="949">
@@ -25978,13 +25978,13 @@
         </is>
       </c>
       <c r="E949">
-        <v>0.9794751835827444</v>
+        <v>1.101909581530587</v>
       </c>
       <c r="F949">
-        <v>-0.9644742152869671</v>
+        <v>-1.085033492197838</v>
       </c>
       <c r="G949">
-        <v>3.005127757401485</v>
+        <v>3.38076872707667</v>
       </c>
     </row>
     <row r="950">
@@ -26140,13 +26140,13 @@
         </is>
       </c>
       <c r="E955">
-        <v>3.978304242518192</v>
+        <v>4.420338047242435</v>
       </c>
       <c r="F955">
-        <v>0.6376187389165637</v>
+        <v>0.7084652654628486</v>
       </c>
       <c r="G955">
-        <v>7.657228478346854</v>
+        <v>8.508031642607616</v>
       </c>
     </row>
     <row r="956">
@@ -26167,13 +26167,13 @@
         </is>
       </c>
       <c r="E956">
-        <v>0.3657255193804041</v>
+        <v>0.4876340258405388</v>
       </c>
       <c r="F956">
-        <v>-0.4146546203590485</v>
+        <v>-0.552872827145398</v>
       </c>
       <c r="G956">
-        <v>1.159612569812146</v>
+        <v>1.546150093082861</v>
       </c>
     </row>
     <row r="957">
@@ -26302,13 +26302,13 @@
         </is>
       </c>
       <c r="E961">
-        <v>3.934328886585669</v>
+        <v>4.496375870383622</v>
       </c>
       <c r="F961">
-        <v>1.471631674862578</v>
+        <v>1.681864771271518</v>
       </c>
       <c r="G961">
-        <v>6.478993311616431</v>
+        <v>7.404563784704493</v>
       </c>
     </row>
     <row r="962">
@@ -26491,13 +26491,13 @@
         </is>
       </c>
       <c r="E968">
-        <v>3.128696415319414</v>
+        <v>4.550831149555511</v>
       </c>
       <c r="F968">
-        <v>1.077689106109377</v>
+        <v>1.567547790704548</v>
       </c>
       <c r="G968">
-        <v>5.222381281751705</v>
+        <v>7.596190955275207</v>
       </c>
     </row>
     <row r="969">
@@ -26518,13 +26518,13 @@
         </is>
       </c>
       <c r="E969">
-        <v>0.9361959177182677</v>
+        <v>1.203680465637773</v>
       </c>
       <c r="F969">
-        <v>-0.825641824320287</v>
+        <v>-1.061539488411797</v>
       </c>
       <c r="G969">
-        <v>2.737714720134914</v>
+        <v>3.519918925887747</v>
       </c>
     </row>
     <row r="970">
@@ -26680,13 +26680,13 @@
         </is>
       </c>
       <c r="E975">
-        <v>5.054645745262891</v>
+        <v>5.307378032526036</v>
       </c>
       <c r="F975">
-        <v>0.9001621178435609</v>
+        <v>0.945170223735739</v>
       </c>
       <c r="G975">
-        <v>9.281312764156473</v>
+        <v>9.745378402364297</v>
       </c>
     </row>
     <row r="976">
@@ -26707,13 +26707,13 @@
         </is>
       </c>
       <c r="E976">
-        <v>0.8304285279404493</v>
+        <v>1.522452301224157</v>
       </c>
       <c r="F976">
-        <v>-0.6937274295852047</v>
+        <v>-1.271833620906209</v>
       </c>
       <c r="G976">
-        <v>2.405289224008194</v>
+        <v>4.409696910681689</v>
       </c>
     </row>
     <row r="977">
@@ -26842,13 +26842,13 @@
         </is>
       </c>
       <c r="E981">
-        <v>1.938094358637596</v>
+        <v>2.422617948296995</v>
       </c>
       <c r="F981">
-        <v>0.7717519565157034</v>
+        <v>0.9646899456446292</v>
       </c>
       <c r="G981">
-        <v>3.29921870353116</v>
+        <v>4.124023379413949</v>
       </c>
     </row>
     <row r="982">
@@ -27004,13 +27004,13 @@
         </is>
       </c>
       <c r="E987">
-        <v>3.325657151782237</v>
+        <v>3.627989620126077</v>
       </c>
       <c r="F987">
-        <v>1.751496872533031</v>
+        <v>1.910723860945124</v>
       </c>
       <c r="G987">
-        <v>4.945408423477089</v>
+        <v>5.394991007429551</v>
       </c>
     </row>
     <row r="988">
@@ -27112,13 +27112,13 @@
         </is>
       </c>
       <c r="E991">
-        <v>2.047556710970834</v>
+        <v>2.502569313408797</v>
       </c>
       <c r="F991">
-        <v>0.3297779715485682</v>
+        <v>0.4030619652260278</v>
       </c>
       <c r="G991">
-        <v>3.895072502491124</v>
+        <v>4.760644169711373</v>
       </c>
     </row>
     <row r="992">
@@ -27274,13 +27274,13 @@
         </is>
       </c>
       <c r="E997">
-        <v>2.210169023621217</v>
+        <v>2.652202828345461</v>
       </c>
       <c r="F997">
-        <v>0.3542326327314243</v>
+        <v>0.4250791592777091</v>
       </c>
       <c r="G997">
-        <v>4.254015821303808</v>
+        <v>5.104818985564569</v>
       </c>
     </row>
     <row r="998">
@@ -27301,13 +27301,13 @@
         </is>
       </c>
       <c r="E998">
-        <v>0.1219085064601347</v>
+        <v>0.2438170129202694</v>
       </c>
       <c r="F998">
-        <v>-0.1382182067863495</v>
+        <v>-0.276436413572699</v>
       </c>
       <c r="G998">
-        <v>0.3865375232707153</v>
+        <v>0.7730750465414306</v>
       </c>
     </row>
     <row r="999">
@@ -27436,13 +27436,13 @@
         </is>
       </c>
       <c r="E1003">
-        <v>3.934328886585669</v>
+        <v>5.339446346080551</v>
       </c>
       <c r="F1003">
-        <v>1.471631674862578</v>
+        <v>1.997214415884927</v>
       </c>
       <c r="G1003">
-        <v>6.478993311616431</v>
+        <v>8.792919494336585</v>
       </c>
     </row>
     <row r="1004">
@@ -27463,13 +27463,13 @@
         </is>
       </c>
       <c r="E1004">
-        <v>0.4338597048495973</v>
+        <v>0.7230995080826623</v>
       </c>
       <c r="F1004">
-        <v>-0.3590782077895925</v>
+        <v>-0.5984636796493209</v>
       </c>
       <c r="G1004">
-        <v>1.224628944541903</v>
+        <v>2.041048240903172</v>
       </c>
     </row>
     <row r="1005">
@@ -27598,13 +27598,13 @@
         </is>
       </c>
       <c r="E1009">
-        <v>4.83525809640273</v>
+        <v>5.404111990097169</v>
       </c>
       <c r="F1009">
-        <v>1.665519527623582</v>
+        <v>1.861463001461651</v>
       </c>
       <c r="G1009">
-        <v>8.070952889979909</v>
+        <v>9.020476759389309</v>
       </c>
     </row>
     <row r="1010">
@@ -27733,13 +27733,13 @@
         </is>
       </c>
       <c r="E1014">
-        <v>1.769126010842012</v>
+        <v>3.032787447157735</v>
       </c>
       <c r="F1014">
-        <v>0.3150567412452463</v>
+        <v>0.5400972707061366</v>
       </c>
       <c r="G1014">
-        <v>3.248459467454766</v>
+        <v>5.568787658493884</v>
       </c>
     </row>
     <row r="1015">
@@ -27922,13 +27922,13 @@
         </is>
       </c>
       <c r="E1021">
-        <v>3.608405116709154</v>
+        <v>4.941946138101668</v>
       </c>
       <c r="F1021">
-        <v>2.133073487034642</v>
+        <v>2.921383253982226</v>
       </c>
       <c r="G1021">
-        <v>5.225113156200154</v>
+        <v>7.156133235665427</v>
       </c>
     </row>
     <row r="1022">
@@ -27949,13 +27949,13 @@
         </is>
       </c>
       <c r="E1022">
-        <v>8.298735575384088</v>
+        <v>10.50308721259549</v>
       </c>
       <c r="F1022">
-        <v>5.579690535888278</v>
+        <v>7.061795834483602</v>
       </c>
       <c r="G1022">
-        <v>11.12661919874357</v>
+        <v>14.08212742340983</v>
       </c>
     </row>
     <row r="1023">
@@ -28084,13 +28084,13 @@
         </is>
       </c>
       <c r="E1027">
-        <v>5.61241612204548</v>
+        <v>7.874136051825002</v>
       </c>
       <c r="F1027">
-        <v>3.395303264479427</v>
+        <v>4.763559803896509</v>
       </c>
       <c r="G1027">
-        <v>7.951743769961301</v>
+        <v>11.15617782651287</v>
       </c>
     </row>
     <row r="1028">
@@ -28111,13 +28111,13 @@
         </is>
       </c>
       <c r="E1028">
-        <v>9.442274214287229</v>
+        <v>11.80284276785904</v>
       </c>
       <c r="F1028">
-        <v>6.368913084953015</v>
+        <v>7.961141356191269</v>
       </c>
       <c r="G1028">
-        <v>12.67859428708874</v>
+        <v>15.84824285886092</v>
       </c>
     </row>
     <row r="1029">
@@ -28300,13 +28300,13 @@
         </is>
       </c>
       <c r="E1035">
-        <v>7.75774086669441</v>
+        <v>9.5830916588578</v>
       </c>
       <c r="F1035">
-        <v>4.434758022028574</v>
+        <v>5.478230497800003</v>
       </c>
       <c r="G1035">
-        <v>11.18531669978491</v>
+        <v>13.81715592326372</v>
       </c>
     </row>
     <row r="1036">
@@ -28327,13 +28327,13 @@
         </is>
       </c>
       <c r="E1036">
-        <v>15.4506689697387</v>
+        <v>18.50861386999948</v>
       </c>
       <c r="F1036">
-        <v>10.53885396101189</v>
+        <v>12.62466880746216</v>
       </c>
       <c r="G1036">
-        <v>20.48227138437868</v>
+        <v>24.53605426253696</v>
       </c>
     </row>
     <row r="1037">
@@ -28462,13 +28462,13 @@
         </is>
       </c>
       <c r="E1041">
-        <v>9.443302716933594</v>
+        <v>11.22505794654371</v>
       </c>
       <c r="F1041">
-        <v>5.366385789105606</v>
+        <v>6.378911409691569</v>
       </c>
       <c r="G1041">
-        <v>13.66110262050368</v>
+        <v>16.23866915267418</v>
       </c>
     </row>
     <row r="1042">
@@ -28489,13 +28489,13 @@
         </is>
       </c>
       <c r="E1042">
-        <v>14.57957883072014</v>
+        <v>18.09878751399741</v>
       </c>
       <c r="F1042">
-        <v>9.904018696032868</v>
+        <v>12.29464389852356</v>
       </c>
       <c r="G1042">
-        <v>19.14940485401253</v>
+        <v>23.77167499118797</v>
       </c>
     </row>
     <row r="1043">
@@ -28624,13 +28624,13 @@
         </is>
       </c>
       <c r="E1047">
-        <v>7.954962912674385</v>
+        <v>10.79602109577238</v>
       </c>
       <c r="F1047">
-        <v>4.683344940708135</v>
+        <v>6.355968133818184</v>
       </c>
       <c r="G1047">
-        <v>11.23797334875679</v>
+        <v>15.25153525902708</v>
       </c>
     </row>
     <row r="1048">
@@ -28651,13 +28651,13 @@
         </is>
       </c>
       <c r="E1048">
-        <v>17.12104324157961</v>
+        <v>19.61786204764331</v>
       </c>
       <c r="F1048">
-        <v>11.97981267376605</v>
+        <v>13.72686868869026</v>
       </c>
       <c r="G1048">
-        <v>22.41481353494946</v>
+        <v>25.68364050879626</v>
       </c>
     </row>
     <row r="1049">
@@ -28813,13 +28813,13 @@
         </is>
       </c>
       <c r="E1054">
-        <v>10.35400262144773</v>
+        <v>13.1416187118375</v>
       </c>
       <c r="F1054">
-        <v>6.04594046178009</v>
+        <v>7.673693663028576</v>
       </c>
       <c r="G1054">
-        <v>14.76802351361763</v>
+        <v>18.74402984420699</v>
       </c>
     </row>
     <row r="1055">
@@ -28840,13 +28840,13 @@
         </is>
       </c>
       <c r="E1055">
-        <v>16.40565570684043</v>
+        <v>21.70331536217432</v>
       </c>
       <c r="F1055">
-        <v>11.44299340066141</v>
+        <v>15.13812668629166</v>
       </c>
       <c r="G1055">
-        <v>21.38468453639863</v>
+        <v>28.29015558461069</v>
       </c>
     </row>
     <row r="1056">
@@ -29002,13 +29002,13 @@
         </is>
       </c>
       <c r="E1061">
-        <v>9.009643151522569</v>
+        <v>10.83181817093163</v>
       </c>
       <c r="F1061">
-        <v>5.113772656906015</v>
+        <v>6.148018812235321</v>
       </c>
       <c r="G1061">
-        <v>12.90866914116151</v>
+        <v>15.51941121465484</v>
       </c>
     </row>
     <row r="1062">
@@ -29029,13 +29029,13 @@
         </is>
       </c>
       <c r="E1062">
-        <v>16.31927186107863</v>
+        <v>22.09901397854398</v>
       </c>
       <c r="F1062">
-        <v>11.16772879242254</v>
+        <v>15.1229660730722</v>
       </c>
       <c r="G1062">
-        <v>21.47838730607461</v>
+        <v>29.0853161436427</v>
       </c>
     </row>
     <row r="1063">
@@ -29218,13 +29218,13 @@
         </is>
       </c>
       <c r="E1069">
-        <v>26.98390237517756</v>
+        <v>31.43995964814266</v>
       </c>
       <c r="F1069">
-        <v>13.76590854344731</v>
+        <v>16.03917784420008</v>
       </c>
       <c r="G1069">
-        <v>42.01901786529062</v>
+        <v>48.95793824671476</v>
       </c>
     </row>
     <row r="1070">
@@ -29245,13 +29245,13 @@
         </is>
       </c>
       <c r="E1070">
-        <v>2.754526028173436</v>
+        <v>3.078587913840899</v>
       </c>
       <c r="F1070">
-        <v>1.268001636104116</v>
+        <v>1.417178299175189</v>
       </c>
       <c r="G1070">
-        <v>4.938878079602408</v>
+        <v>5.519922559555633</v>
       </c>
     </row>
     <row r="1071">
@@ -29434,13 +29434,13 @@
         </is>
       </c>
       <c r="E1077">
-        <v>26.50930298893417</v>
+        <v>33.0013771903058</v>
       </c>
       <c r="F1077">
-        <v>13.95318424992007</v>
+        <v>17.37029059683928</v>
       </c>
       <c r="G1077">
-        <v>40.30428894600052</v>
+        <v>50.17472705522513</v>
       </c>
     </row>
     <row r="1078">
@@ -29461,13 +29461,13 @@
         </is>
       </c>
       <c r="E1078">
-        <v>2.741812616510127</v>
+        <v>3.655750155346836</v>
       </c>
       <c r="F1078">
-        <v>1.305844624247305</v>
+        <v>1.741126165663073</v>
       </c>
       <c r="G1078">
-        <v>4.698113235525988</v>
+        <v>6.264150980701317</v>
       </c>
     </row>
     <row r="1079">
@@ -29650,13 +29650,13 @@
         </is>
       </c>
       <c r="E1085">
-        <v>28.59487541409389</v>
+        <v>32.94129647703615</v>
       </c>
       <c r="F1085">
-        <v>14.14014662327382</v>
+        <v>16.28944891001144</v>
       </c>
       <c r="G1085">
-        <v>45.20368207316086</v>
+        <v>52.0746417482813</v>
       </c>
     </row>
     <row r="1086">
@@ -29677,13 +29677,13 @@
         </is>
       </c>
       <c r="E1086">
-        <v>4.005052733895959</v>
+        <v>4.450058593217732</v>
       </c>
       <c r="F1086">
-        <v>1.856587048020558</v>
+        <v>2.06287449780062</v>
       </c>
       <c r="G1086">
-        <v>6.742824042904383</v>
+        <v>7.492026714338203</v>
       </c>
     </row>
     <row r="1087">
@@ -29866,13 +29866,13 @@
         </is>
       </c>
       <c r="E1093">
-        <v>22.4742701092279</v>
+        <v>27.27214799771476</v>
       </c>
       <c r="F1093">
-        <v>11.2690619437534</v>
+        <v>13.67481674073446</v>
       </c>
       <c r="G1093">
-        <v>34.78102764001842</v>
+        <v>42.2061908440673</v>
       </c>
     </row>
     <row r="1094">
@@ -29893,13 +29893,13 @@
         </is>
       </c>
       <c r="E1094">
-        <v>5.285081834231681</v>
+        <v>5.796541366576682</v>
       </c>
       <c r="F1094">
-        <v>2.470091417459434</v>
+        <v>2.709132522374863</v>
       </c>
       <c r="G1094">
-        <v>8.853252778641783</v>
+        <v>9.710019176574859</v>
       </c>
     </row>
     <row r="1095">
@@ -30082,13 +30082,13 @@
         </is>
       </c>
       <c r="E1101">
-        <v>24.03290573860238</v>
+        <v>26.19316692858911</v>
       </c>
       <c r="F1101">
-        <v>12.49476116685258</v>
+        <v>13.61788576612023</v>
       </c>
       <c r="G1101">
-        <v>36.61785697385361</v>
+        <v>39.90934973554831</v>
       </c>
     </row>
     <row r="1102">
@@ -30109,13 +30109,13 @@
         </is>
       </c>
       <c r="E1102">
-        <v>2.298979123938374</v>
+        <v>2.682142311261436</v>
       </c>
       <c r="F1102">
-        <v>1.071805971498847</v>
+        <v>1.250440300081988</v>
       </c>
       <c r="G1102">
-        <v>3.946876167240482</v>
+        <v>4.604688861780562</v>
       </c>
     </row>
     <row r="1103">
@@ -30298,13 +30298,13 @@
         </is>
       </c>
       <c r="E1109">
-        <v>33.19462288529159</v>
+        <v>38.47558561704253</v>
       </c>
       <c r="F1109">
-        <v>17.36049057930534</v>
+        <v>20.12238680783119</v>
       </c>
       <c r="G1109">
-        <v>50.98787782119095</v>
+        <v>59.09958565638042</v>
       </c>
     </row>
     <row r="1110">
@@ -30325,13 +30325,13 @@
         </is>
       </c>
       <c r="E1110">
-        <v>3.490960854078617</v>
+        <v>4.333606577476904</v>
       </c>
       <c r="F1110">
-        <v>1.623810095459828</v>
+        <v>2.01576425643289</v>
       </c>
       <c r="G1110">
-        <v>6.041686680554109</v>
+        <v>7.500024844825791</v>
       </c>
     </row>
     <row r="1111">
@@ -30514,13 +30514,13 @@
         </is>
       </c>
       <c r="E1117">
-        <v>16.15466455511449</v>
+        <v>18.75426574789153</v>
       </c>
       <c r="F1117">
-        <v>8.040376323934019</v>
+        <v>9.334229985256735</v>
       </c>
       <c r="G1117">
-        <v>25.90829279843219</v>
+        <v>30.07744336369714</v>
       </c>
     </row>
     <row r="1118">
@@ -30541,13 +30541,13 @@
         </is>
       </c>
       <c r="E1118">
-        <v>1.778698772337129</v>
+        <v>2.032798596956719</v>
       </c>
       <c r="F1118">
-        <v>0.8150496331916157</v>
+        <v>0.9314852950761323</v>
       </c>
       <c r="G1118">
-        <v>3.171857923167074</v>
+        <v>3.624980483619513</v>
       </c>
     </row>
     <row r="1119">
@@ -30730,13 +30730,13 @@
         </is>
       </c>
       <c r="E1125">
-        <v>16.81637702285096</v>
+        <v>20.66419210435075</v>
       </c>
       <c r="F1125">
-        <v>8.859926008281574</v>
+        <v>10.88719721356634</v>
       </c>
       <c r="G1125">
-        <v>25.39676585417801</v>
+        <v>31.20789024454078</v>
       </c>
     </row>
     <row r="1126">
@@ -30757,13 +30757,13 @@
         </is>
       </c>
       <c r="E1126">
-        <v>12.34334885985076</v>
+        <v>15.2701223008463</v>
       </c>
       <c r="F1126">
-        <v>8.191468561189481</v>
+        <v>10.13377553961585</v>
       </c>
       <c r="G1126">
-        <v>16.66146243104937</v>
+        <v>20.61211847140128</v>
       </c>
     </row>
     <row r="1127">
@@ -30946,13 +30946,13 @@
         </is>
       </c>
       <c r="E1133">
-        <v>18.61858012657358</v>
+        <v>22.37294402040941</v>
       </c>
       <c r="F1133">
-        <v>10.0198050928053</v>
+        <v>12.04025961769196</v>
       </c>
       <c r="G1133">
-        <v>27.56187481413209</v>
+        <v>33.11961911821634</v>
       </c>
     </row>
     <row r="1134">
@@ -30973,13 +30973,13 @@
         </is>
       </c>
       <c r="E1134">
-        <v>11.07713843692224</v>
+        <v>13.7788795190984</v>
       </c>
       <c r="F1134">
-        <v>7.288443547321359</v>
+        <v>9.066112705204617</v>
       </c>
       <c r="G1134">
-        <v>15.03846098865194</v>
+        <v>18.70637830295729</v>
       </c>
     </row>
     <row r="1135">
@@ -31162,13 +31162,13 @@
         </is>
       </c>
       <c r="E1141">
-        <v>22.45002197194869</v>
+        <v>25.64515618518483</v>
       </c>
       <c r="F1141">
-        <v>11.69725280870698</v>
+        <v>13.3620303620061</v>
       </c>
       <c r="G1141">
-        <v>33.5210698313013</v>
+        <v>38.2918587960558</v>
       </c>
     </row>
     <row r="1142">
@@ -31189,13 +31189,13 @@
         </is>
       </c>
       <c r="E1142">
-        <v>12.80036561321675</v>
+        <v>15.32883289483981</v>
       </c>
       <c r="F1142">
-        <v>8.644210292296977</v>
+        <v>10.35170862163959</v>
       </c>
       <c r="G1142">
-        <v>17.07899545827408</v>
+        <v>20.45262419077266</v>
       </c>
     </row>
     <row r="1143">
@@ -31378,13 +31378,13 @@
         </is>
       </c>
       <c r="E1149">
-        <v>22.14287271721173</v>
+        <v>27.14552173850772</v>
       </c>
       <c r="F1149">
-        <v>11.3539681977461</v>
+        <v>13.9191239757554</v>
       </c>
       <c r="G1149">
-        <v>33.20700943490675</v>
+        <v>40.70933378871901</v>
       </c>
     </row>
     <row r="1150">
@@ -31405,13 +31405,13 @@
         </is>
       </c>
       <c r="E1150">
-        <v>13.71035236518815</v>
+        <v>16.35331185727261</v>
       </c>
       <c r="F1150">
-        <v>9.204666525339944</v>
+        <v>10.97906007239343</v>
       </c>
       <c r="G1150">
-        <v>18.09875038970672</v>
+        <v>21.58766612748151</v>
       </c>
     </row>
     <row r="1151">
@@ -31594,13 +31594,13 @@
         </is>
       </c>
       <c r="E1157">
-        <v>21.4616188415716</v>
+        <v>26.56740719501001</v>
       </c>
       <c r="F1157">
-        <v>11.2050837332391</v>
+        <v>13.87080929880808</v>
       </c>
       <c r="G1157">
-        <v>31.62116807187412</v>
+        <v>39.14394595994094</v>
       </c>
     </row>
     <row r="1158">
@@ -31621,13 +31621,13 @@
         </is>
       </c>
       <c r="E1158">
-        <v>14.56117381513207</v>
+        <v>17.89445456799363</v>
       </c>
       <c r="F1158">
-        <v>10.05857728870057</v>
+        <v>12.36114317406576</v>
       </c>
       <c r="G1158">
-        <v>19.18648838966488</v>
+        <v>23.57857609332311</v>
       </c>
     </row>
     <row r="1159">
@@ -31810,13 +31810,13 @@
         </is>
       </c>
       <c r="E1165">
-        <v>22.38807258419387</v>
+        <v>28.1504035024885</v>
       </c>
       <c r="F1165">
-        <v>12.29797323620513</v>
+        <v>15.46327436451109</v>
       </c>
       <c r="G1165">
-        <v>32.67360878948552</v>
+        <v>41.08327181125183</v>
       </c>
     </row>
     <row r="1166">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="E1166">
-        <v>15.67098781678942</v>
+        <v>17.8615560062331</v>
       </c>
       <c r="F1166">
-        <v>10.86799097058994</v>
+        <v>12.38717250411327</v>
       </c>
       <c r="G1166">
-        <v>20.53782510442921</v>
+        <v>23.40870388246771</v>
       </c>
     </row>
     <row r="1167">
@@ -32026,13 +32026,13 @@
         </is>
       </c>
       <c r="E1173">
-        <v>22.81077718089725</v>
+        <v>27.66413402789667</v>
       </c>
       <c r="F1173">
-        <v>12.27526942372922</v>
+        <v>14.8870288755865</v>
       </c>
       <c r="G1173">
-        <v>33.32217497584303</v>
+        <v>40.41199943878836</v>
       </c>
     </row>
     <row r="1174">
@@ -32053,13 +32053,13 @@
         </is>
       </c>
       <c r="E1174">
-        <v>14.65585618681888</v>
+        <v>17.0142698260771</v>
       </c>
       <c r="F1174">
-        <v>9.969598834706343</v>
+        <v>11.57390209546369</v>
       </c>
       <c r="G1174">
-        <v>19.34968578962838</v>
+        <v>22.46342833048812</v>
       </c>
     </row>
     <row r="1175">
@@ -32242,13 +32242,13 @@
         </is>
       </c>
       <c r="E1181">
-        <v>3.627897777891589</v>
+        <v>5.290684259425234</v>
       </c>
       <c r="F1181">
-        <v>0.5775966739791476</v>
+        <v>0.8423284828862569</v>
       </c>
       <c r="G1181">
-        <v>8.76227090138701</v>
+        <v>12.77831173118939</v>
       </c>
     </row>
     <row r="1182">
@@ -32269,13 +32269,13 @@
         </is>
       </c>
       <c r="E1182">
-        <v>0.4709908185674817</v>
+        <v>0.5494892883287287</v>
       </c>
       <c r="F1182">
-        <v>0.0788905129493547</v>
+        <v>0.09203893177424714</v>
       </c>
       <c r="G1182">
-        <v>1.15398840159332</v>
+        <v>1.346319801858873</v>
       </c>
     </row>
     <row r="1183">
@@ -32458,13 +32458,13 @@
         </is>
       </c>
       <c r="E1189">
-        <v>3.918515301433904</v>
+        <v>5.155941186097242</v>
       </c>
       <c r="F1189">
-        <v>0.6239175301260965</v>
+        <v>0.820944118586969</v>
       </c>
       <c r="G1189">
-        <v>9.293220605417453</v>
+        <v>12.22792184923349</v>
       </c>
     </row>
     <row r="1190">
@@ -32674,13 +32674,13 @@
         </is>
       </c>
       <c r="E1197">
-        <v>3.617411441051352</v>
+        <v>3.87579797255502</v>
       </c>
       <c r="F1197">
-        <v>0.6425523116156175</v>
+        <v>0.6884489053024473</v>
       </c>
       <c r="G1197">
-        <v>8.514427899178589</v>
+        <v>9.122601320548489</v>
       </c>
     </row>
     <row r="1198">
@@ -32701,13 +32701,13 @@
         </is>
       </c>
       <c r="E1198">
-        <v>0.4809955643316481</v>
+        <v>0.5919945407158747</v>
       </c>
       <c r="F1198">
-        <v>0.09683158647702397</v>
+        <v>0.119177337202491</v>
       </c>
       <c r="G1198">
-        <v>0.9931623660104768</v>
+        <v>1.222353681243664</v>
       </c>
     </row>
     <row r="1199">
@@ -32890,13 +32890,13 @@
         </is>
       </c>
       <c r="E1205">
-        <v>2.740969268838092</v>
+        <v>3.239327317717745</v>
       </c>
       <c r="F1205">
-        <v>0.473727843414205</v>
+        <v>0.5598601785804241</v>
       </c>
       <c r="G1205">
-        <v>6.529562076024488</v>
+        <v>7.716755180756214</v>
       </c>
     </row>
     <row r="1206">
@@ -33106,13 +33106,13 @@
         </is>
       </c>
       <c r="E1213">
-        <v>2.852881877166671</v>
+        <v>3.566102346458338</v>
       </c>
       <c r="F1213">
-        <v>0.4994801158479946</v>
+        <v>0.6243501448099932</v>
       </c>
       <c r="G1213">
-        <v>6.765179565434802</v>
+        <v>8.456474456793503</v>
       </c>
     </row>
     <row r="1214">
@@ -33133,13 +33133,13 @@
         </is>
       </c>
       <c r="E1214">
-        <v>0.2918849041892481</v>
+        <v>0.3405323882207895</v>
       </c>
       <c r="F1214">
-        <v>0.05163214567639918</v>
+        <v>0.06023750328913238</v>
       </c>
       <c r="G1214">
-        <v>0.7093980330127898</v>
+        <v>0.8276310385149214</v>
       </c>
     </row>
     <row r="1215">
@@ -33322,13 +33322,13 @@
         </is>
       </c>
       <c r="E1221">
-        <v>4.49958619442687</v>
+        <v>5.399503433312243</v>
       </c>
       <c r="F1221">
-        <v>0.675318542181215</v>
+        <v>0.8103822506174581</v>
       </c>
       <c r="G1221">
-        <v>11.22132835292071</v>
+        <v>13.46559402350485</v>
       </c>
     </row>
     <row r="1222">
@@ -33349,13 +33349,13 @@
         </is>
       </c>
       <c r="E1222">
-        <v>0.2952166319628091</v>
+        <v>0.3373904365289247</v>
       </c>
       <c r="F1222">
-        <v>0.04963529225914063</v>
+        <v>0.05672604829616072</v>
       </c>
       <c r="G1222">
-        <v>0.7057269605242877</v>
+        <v>0.8065450977420431</v>
       </c>
     </row>
     <row r="1223">
@@ -33538,13 +33538,13 @@
         </is>
       </c>
       <c r="E1229">
-        <v>4.437833791482472</v>
+        <v>5.17747275672955</v>
       </c>
       <c r="F1229">
-        <v>0.6389769769792127</v>
+        <v>0.7454731398090816</v>
       </c>
       <c r="G1229">
-        <v>11.66751235427664</v>
+        <v>13.61209774665608</v>
       </c>
     </row>
     <row r="1230">
@@ -33754,13 +33754,13 @@
         </is>
       </c>
       <c r="E1237">
-        <v>22.03622652744067</v>
+        <v>25.59592465879647</v>
       </c>
       <c r="F1237">
-        <v>9.615877183966486</v>
+        <v>11.16921119060723</v>
       </c>
       <c r="G1237">
-        <v>36.78227256351736</v>
+        <v>42.72402428531632</v>
       </c>
     </row>
     <row r="1238">
@@ -33781,13 +33781,13 @@
         </is>
       </c>
       <c r="E1238">
-        <v>0.7333802335523772</v>
+        <v>0.9953017455353691</v>
       </c>
       <c r="F1238">
-        <v>0.2969250636455667</v>
+        <v>0.4029697292332691</v>
       </c>
       <c r="G1238">
-        <v>1.365000555784408</v>
+        <v>1.85250075427884</v>
       </c>
     </row>
     <row r="1239">
@@ -33970,13 +33970,13 @@
         </is>
       </c>
       <c r="E1245">
-        <v>27.82133607381563</v>
+        <v>34.35654924551728</v>
       </c>
       <c r="F1245">
-        <v>12.60185840724025</v>
+        <v>15.56202648947789</v>
       </c>
       <c r="G1245">
-        <v>45.32751705521515</v>
+        <v>55.97492039033281</v>
       </c>
     </row>
     <row r="1246">
@@ -33997,13 +33997,13 @@
         </is>
       </c>
       <c r="E1246">
-        <v>4.148319460839209</v>
+        <v>4.755390601449825</v>
       </c>
       <c r="F1246">
-        <v>1.726476103558884</v>
+        <v>1.979131143104086</v>
       </c>
       <c r="G1246">
-        <v>7.499448138610543</v>
+        <v>8.596928354016963</v>
       </c>
     </row>
     <row r="1247">
@@ -34186,13 +34186,13 @@
         </is>
       </c>
       <c r="E1253">
-        <v>21.67337464084184</v>
+        <v>26.81885207355968</v>
       </c>
       <c r="F1253">
-        <v>9.17774373445673</v>
+        <v>11.35663253472343</v>
       </c>
       <c r="G1253">
-        <v>36.60936043738661</v>
+        <v>45.3007913325935</v>
       </c>
     </row>
     <row r="1254">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="E1254">
-        <v>3.159446969324673</v>
+        <v>4.048041429447237</v>
       </c>
       <c r="F1254">
-        <v>1.259645473099482</v>
+        <v>1.613920762408711</v>
       </c>
       <c r="G1254">
-        <v>5.603543740566867</v>
+        <v>7.179540417601298</v>
       </c>
     </row>
     <row r="1255">
@@ -34402,13 +34402,13 @@
         </is>
       </c>
       <c r="E1261">
-        <v>27.12927600704589</v>
+        <v>31.6508220082202</v>
       </c>
       <c r="F1261">
-        <v>11.62733675343653</v>
+        <v>13.56522621234262</v>
       </c>
       <c r="G1261">
-        <v>44.93274820817226</v>
+        <v>52.42153957620096</v>
       </c>
     </row>
     <row r="1262">
@@ -34429,13 +34429,13 @@
         </is>
       </c>
       <c r="E1262">
-        <v>4.459377494274365</v>
+        <v>5.602807621011382</v>
       </c>
       <c r="F1262">
-        <v>1.786265111203444</v>
+        <v>2.244281806383815</v>
       </c>
       <c r="G1262">
-        <v>7.906827321572888</v>
+        <v>9.934218942489014</v>
       </c>
     </row>
     <row r="1263">
@@ -34618,13 +34618,13 @@
         </is>
       </c>
       <c r="E1269">
-        <v>35.94372520845457</v>
+        <v>41.90330659016725</v>
       </c>
       <c r="F1269">
-        <v>16.05994933846127</v>
+        <v>18.72273886608179</v>
       </c>
       <c r="G1269">
-        <v>58.81572495180896</v>
+        <v>68.56755499563221</v>
       </c>
     </row>
     <row r="1270">
@@ -34645,13 +34645,13 @@
         </is>
       </c>
       <c r="E1270">
-        <v>3.868342303384221</v>
+        <v>4.793380680280448</v>
       </c>
       <c r="F1270">
-        <v>1.559371782956517</v>
+        <v>1.93226503540264</v>
       </c>
       <c r="G1270">
-        <v>6.967199635974175</v>
+        <v>8.633269114141912</v>
       </c>
     </row>
     <row r="1271">
@@ -34834,13 +34834,13 @@
         </is>
       </c>
       <c r="E1277">
-        <v>29.39502865963666</v>
+        <v>34.89585273629381</v>
       </c>
       <c r="F1277">
-        <v>13.25305961933144</v>
+        <v>15.73316434341685</v>
       </c>
       <c r="G1277">
-        <v>48.30834288555641</v>
+        <v>57.34850061852604</v>
       </c>
     </row>
     <row r="1278">
@@ -34861,13 +34861,13 @@
         </is>
       </c>
       <c r="E1278">
-        <v>3.316405529232854</v>
+        <v>3.632253674874078</v>
       </c>
       <c r="F1278">
-        <v>1.324820184521678</v>
+        <v>1.450993535428504</v>
       </c>
       <c r="G1278">
-        <v>6.009437242106182</v>
+        <v>6.581764598497248</v>
       </c>
     </row>
     <row r="1279">
@@ -35050,13 +35050,13 @@
         </is>
       </c>
       <c r="E1285">
-        <v>22.6241813026164</v>
+        <v>27.69298694965068</v>
       </c>
       <c r="F1285">
-        <v>9.768364636904508</v>
+        <v>11.95690534790497</v>
       </c>
       <c r="G1285">
-        <v>38.39245554897524</v>
+        <v>46.99404395065822</v>
       </c>
     </row>
     <row r="1286">
@@ -35077,13 +35077,13 @@
         </is>
       </c>
       <c r="E1286">
-        <v>3.220720954892278</v>
+        <v>3.821194353262025</v>
       </c>
       <c r="F1286">
-        <v>1.291787848948242</v>
+        <v>1.532629651294524</v>
       </c>
       <c r="G1286">
-        <v>5.971896215960736</v>
+        <v>7.085300595207652</v>
       </c>
     </row>
   </sheetData>
